--- a/Studies/Journal - Simon Solar captest/plots/2026-08-EPRI_scenarios_SAMresults.xlsx
+++ b/Studies/Journal - Simon Solar captest/plots/2026-08-EPRI_scenarios_SAMresults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmirletz\source\repos\pv_repowering\Studies\Journal - Simon Solar captest\plots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC5D0517-967D-4494-9AAB-F7152701CF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93E59ED-9593-4DCF-A4C4-3CC3F4AFB89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04F1D575-AB74-4BA9-9193-B5993F01A15B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{04F1D575-AB74-4BA9-9193-B5993F01A15B}"/>
   </bookViews>
   <sheets>
     <sheet name="Simon" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
   <si>
     <t>Year</t>
   </si>
@@ -69,6 +69,15 @@
   </si>
   <si>
     <t>Repair</t>
+  </si>
+  <si>
+    <t>Time stamp</t>
+  </si>
+  <si>
+    <t>Total after-tax returns | ($)</t>
+  </si>
+  <si>
+    <t>After-tax cumulative NPV | ($)</t>
   </si>
 </sst>
 </file>
@@ -398,10 +407,10 @@
                   <c:v>-1.0464800000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-4.3150899999999996</c:v>
+                  <c:v>-4.3292599999999997</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1.0450600000000001</c:v>
+                  <c:v>-1.0515300000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -509,10 +518,10 @@
                   <c:v>-1.0464800000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-28.510200000000001</c:v>
+                  <c:v>-23.018799999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-12.5844</c:v>
+                  <c:v>-10.077299999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2.7426200000000001</c:v>
@@ -620,16 +629,16 @@
                   <c:v>-1.0464800000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1.2334099999999999</c:v>
+                  <c:v>-3.6678099999999998</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.13131699999999999</c:v>
+                  <c:v>-1.24272</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1.86574</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.7992699999999999</c:v>
+                  <c:v>1.7992600000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>1.7311799999999999</c:v>
@@ -1130,10 +1139,10 @@
                   <c:v>-2.1688999999999998</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-3.8310399999999998</c:v>
+                  <c:v>-3.8365</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-4.2001499999999998</c:v>
+                  <c:v>-4.2079000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1211,49 +1220,49 @@
                   <c:v>-2.1688999999999998</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-13.1509</c:v>
+                  <c:v>-11.035600000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-17.595600000000001</c:v>
+                  <c:v>-14.594799999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-16.7074</c:v>
+                  <c:v>-13.7066</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-15.8955</c:v>
+                  <c:v>-12.8947</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-15.153499999999999</c:v>
+                  <c:v>-12.152699999999999</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-14.4781</c:v>
+                  <c:v>-11.477399999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-13.8637</c:v>
+                  <c:v>-10.8629</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-13.3025</c:v>
+                  <c:v>-10.3018</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-12.7903</c:v>
+                  <c:v>-9.7895000000000003</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-12.322699999999999</c:v>
+                  <c:v>-9.3219600000000007</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-11.8971</c:v>
+                  <c:v>-8.8963699999999992</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-11.5099</c:v>
+                  <c:v>-8.5090800000000009</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-11.156700000000001</c:v>
+                  <c:v>-8.1559500000000007</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-10.8348</c:v>
+                  <c:v>-7.8340500000000004</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-10.463699999999999</c:v>
+                  <c:v>-7.4629599999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1331,49 +1340,49 @@
                   <c:v>-2.1688999999999998</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2.6440000000000001</c:v>
+                  <c:v>-3.5817100000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-2.6903800000000002</c:v>
+                  <c:v>-4.0206400000000002</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-2.0861499999999999</c:v>
+                  <c:v>-3.4164099999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1.55186</c:v>
+                  <c:v>-2.88212</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1.08049</c:v>
+                  <c:v>-2.4107500000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-0.66833299999999995</c:v>
+                  <c:v>-1.9985900000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-0.30918499999999999</c:v>
+                  <c:v>-1.63944</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.7341499999999995E-3</c:v>
+                  <c:v>-1.32552</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.278115</c:v>
+                  <c:v>-1.0521400000000001</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.51520200000000005</c:v>
+                  <c:v>-0.81505700000000003</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.71884300000000001</c:v>
+                  <c:v>-0.61141599999999996</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.89267600000000003</c:v>
+                  <c:v>-0.437583</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.0408200000000001</c:v>
+                  <c:v>-0.289439</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.1660999999999999</c:v>
+                  <c:v>-0.164159</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.3488199999999999</c:v>
+                  <c:v>1.8563700000000002E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3076,20 +3085,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A66F2B7E-C15E-4BE7-BAE2-4B1EBEE71C1F}">
-  <dimension ref="A1:Z28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Z69"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.77734375" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
     <col min="7" max="8" width="13" customWidth="1"/>
-    <col min="12" max="12" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9" customWidth="1"/>
-    <col min="17" max="17" width="3.21875" customWidth="1"/>
-    <col min="22" max="22" width="2.77734375" customWidth="1"/>
+    <col min="17" max="17" width="3.28515625" customWidth="1"/>
+    <col min="22" max="22" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -3106,7 +3115,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3174,7 +3183,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0</v>
       </c>
@@ -3255,7 +3264,7 @@
         <v>-13.5573</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3304,11 +3313,11 @@
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="2">
-        <f t="shared" ref="R4:S28" si="3">G4/1000000</f>
+        <f t="shared" ref="R4:R28" si="3">G4/1000000</f>
         <v>-4.4231999999999996</v>
       </c>
       <c r="S4" s="2">
-        <f t="shared" si="3"/>
+        <f>H4/1000000</f>
         <v>-4.4231999999999996</v>
       </c>
       <c r="T4" s="2">
@@ -3336,7 +3345,7 @@
         <v>-3.5956299999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -3389,7 +3398,7 @@
         <v>-2.5281600000000002</v>
       </c>
       <c r="S5" s="2">
-        <f t="shared" si="3"/>
+        <f>H5/1000000</f>
         <v>-2.5281600000000002</v>
       </c>
       <c r="T5" s="2">
@@ -3409,15 +3418,15 @@
         <v>-1.34165</v>
       </c>
       <c r="Y5" s="3">
-        <f>Y4+O5</f>
+        <f t="shared" ref="Y5:Y14" si="7">Y4+O5</f>
         <v>-1.34165</v>
       </c>
       <c r="Z5" s="3">
-        <f>Z4+P5</f>
+        <f t="shared" ref="Z5:Z14" si="8">Z4+P5</f>
         <v>-1.34165</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -3470,7 +3479,7 @@
         <v>-1.5206299999999999</v>
       </c>
       <c r="S6" s="2">
-        <f t="shared" si="3"/>
+        <f>H6/1000000</f>
         <v>-1.5206299999999999</v>
       </c>
       <c r="T6" s="2">
@@ -3490,28 +3499,28 @@
         <v>-3.4720000000000084E-2</v>
       </c>
       <c r="Y6" s="3">
-        <f>Y5+O6</f>
+        <f t="shared" si="7"/>
         <v>-3.4720000000000084E-2</v>
       </c>
       <c r="Z6" s="3">
-        <f>Z5+P6</f>
+        <f t="shared" si="8"/>
         <v>-3.4720000000000084E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" s="1">
         <v>676313</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7">
         <v>676313</v>
       </c>
       <c r="D7" s="1">
         <v>676313</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>676313</v>
       </c>
       <c r="G7" s="1">
@@ -3551,7 +3560,7 @@
         <v>-1.04257</v>
       </c>
       <c r="S7" s="2">
-        <f t="shared" si="3"/>
+        <f>H7/1000000</f>
         <v>-1.04257</v>
       </c>
       <c r="T7" s="2">
@@ -3571,34 +3580,34 @@
         <v>0.64159299999999997</v>
       </c>
       <c r="Y7" s="3">
-        <f>Y6+O7</f>
+        <f t="shared" si="7"/>
         <v>0.64159299999999997</v>
       </c>
       <c r="Z7" s="3">
-        <f>Z6+P7</f>
+        <f t="shared" si="8"/>
         <v>0.64159299999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" s="1">
         <v>522382</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8">
         <v>522382</v>
       </c>
       <c r="D8" s="1">
         <v>522382</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>522382</v>
       </c>
       <c r="G8" s="1">
         <v>-703987</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8">
         <v>-703987</v>
       </c>
       <c r="I8" s="1">
@@ -3632,7 +3641,7 @@
         <v>-0.70398700000000003</v>
       </c>
       <c r="S8" s="2">
-        <f t="shared" si="3"/>
+        <f>H8/1000000</f>
         <v>-0.70398700000000003</v>
       </c>
       <c r="T8" s="2">
@@ -3652,22 +3661,22 @@
         <v>1.163975</v>
       </c>
       <c r="Y8" s="3">
-        <f>Y7+O8</f>
+        <f t="shared" si="7"/>
         <v>1.163975</v>
       </c>
       <c r="Z8" s="3">
-        <f>Z7+P8</f>
+        <f t="shared" si="8"/>
         <v>1.163975</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" s="1">
         <v>2407.9699999999998</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9">
         <v>2407.9699999999998</v>
       </c>
       <c r="D9" s="1">
@@ -3679,7 +3688,7 @@
       <c r="G9" s="1">
         <v>-702556</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9">
         <v>-702556</v>
       </c>
       <c r="I9" s="1">
@@ -3713,7 +3722,7 @@
         <v>-0.70255599999999996</v>
       </c>
       <c r="S9" s="2">
-        <f t="shared" si="3"/>
+        <f>H9/1000000</f>
         <v>-0.70255599999999996</v>
       </c>
       <c r="T9" s="2">
@@ -3733,22 +3742,22 @@
         <v>1.1663829699999999</v>
       </c>
       <c r="Y9" s="3">
-        <f>Y8+O9</f>
+        <f t="shared" si="7"/>
         <v>1.1663829699999999</v>
       </c>
       <c r="Z9" s="3">
-        <f>Z8+P9</f>
+        <f t="shared" si="8"/>
         <v>1.1663829699999999</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10">
         <v>-522389</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>-522389</v>
       </c>
       <c r="D10">
@@ -3760,13 +3769,13 @@
       <c r="G10" s="1">
         <v>-987222</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10">
         <v>-987222</v>
       </c>
       <c r="I10" s="1">
         <v>-987222</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10">
         <v>-987222</v>
       </c>
       <c r="L10">
@@ -3794,7 +3803,7 @@
         <v>-0.98722200000000004</v>
       </c>
       <c r="S10" s="2">
-        <f t="shared" si="3"/>
+        <f>H10/1000000</f>
         <v>-0.98722200000000004</v>
       </c>
       <c r="T10" s="2">
@@ -3814,25 +3823,25 @@
         <v>0.64399396999999992</v>
       </c>
       <c r="Y10" s="3">
-        <f>Y9+O10</f>
+        <f t="shared" si="7"/>
         <v>0.64399396999999992</v>
       </c>
       <c r="Z10" s="3">
-        <f>Z9+P10</f>
+        <f t="shared" si="8"/>
         <v>0.64399396999999992</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11">
         <v>-691240</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>-691240</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>-691240</v>
       </c>
       <c r="E11" s="1">
@@ -3875,7 +3884,7 @@
         <v>-1.3326100000000001</v>
       </c>
       <c r="S11" s="2">
-        <f t="shared" si="3"/>
+        <f>H11/1000000</f>
         <v>-1.3326100000000001</v>
       </c>
       <c r="T11" s="2">
@@ -3895,15 +3904,15 @@
         <v>-4.724603000000005E-2</v>
       </c>
       <c r="Y11" s="3">
-        <f>Y10+O11</f>
+        <f t="shared" si="7"/>
         <v>-4.724603000000005E-2</v>
       </c>
       <c r="Z11" s="3">
-        <f>Z10+P11</f>
+        <f t="shared" si="8"/>
         <v>-4.724603000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -3913,7 +3922,7 @@
       <c r="C12" s="1">
         <v>-865807</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12">
         <v>-865807</v>
       </c>
       <c r="E12" s="1">
@@ -3956,7 +3965,7 @@
         <v>-1.7292799999999999</v>
       </c>
       <c r="S12" s="2">
-        <f t="shared" si="3"/>
+        <f>H12/1000000</f>
         <v>-1.7292799999999999</v>
       </c>
       <c r="T12" s="2">
@@ -3976,15 +3985,15 @@
         <v>-0.91305303000000004</v>
       </c>
       <c r="Y12" s="3">
-        <f>Y11+O12</f>
+        <f t="shared" si="7"/>
         <v>-0.91305303000000004</v>
       </c>
       <c r="Z12" s="3">
-        <f>Z11+P12</f>
+        <f t="shared" si="8"/>
         <v>-0.91305303000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -4037,7 +4046,7 @@
         <v>-2.1688999999999998</v>
       </c>
       <c r="S13" s="2">
-        <f t="shared" si="3"/>
+        <f>H13/1000000</f>
         <v>-2.1688999999999998</v>
       </c>
       <c r="T13" s="2">
@@ -4057,15 +4066,15 @@
         <v>-1.9595330300000002</v>
       </c>
       <c r="Y13" s="3">
-        <f>Y12+O13</f>
+        <f t="shared" si="7"/>
         <v>-1.9595330300000002</v>
       </c>
       <c r="Z13" s="3">
-        <f>Z12+P13</f>
+        <f t="shared" si="8"/>
         <v>-1.9595330300000002</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -4073,25 +4082,25 @@
         <v>-1233410</v>
       </c>
       <c r="C14" s="1">
-        <v>-1233410</v>
+        <v>-3667810</v>
       </c>
       <c r="D14" s="1">
-        <v>-4315090</v>
+        <v>-4329260</v>
       </c>
       <c r="E14" s="1">
-        <v>-28510200</v>
+        <v>-23018800</v>
       </c>
       <c r="G14" s="1">
         <v>-2644000</v>
       </c>
       <c r="H14" s="1">
-        <v>-2644000</v>
+        <v>-3581710</v>
       </c>
       <c r="I14" s="1">
-        <v>-3831040</v>
+        <v>-3836500</v>
       </c>
       <c r="J14" s="1">
-        <v>-13150900</v>
+        <v>-11035600</v>
       </c>
       <c r="L14">
         <v>11</v>
@@ -4102,15 +4111,15 @@
       </c>
       <c r="N14" s="2">
         <f t="shared" si="0"/>
-        <v>-1.2334099999999999</v>
+        <v>-3.6678099999999998</v>
       </c>
       <c r="O14" s="2">
         <f t="shared" si="1"/>
-        <v>-4.3150899999999996</v>
+        <v>-4.3292599999999997</v>
       </c>
       <c r="P14" s="2">
         <f t="shared" si="2"/>
-        <v>-28.510200000000001</v>
+        <v>-23.018799999999999</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2">
@@ -4118,16 +4127,16 @@
         <v>-2.6440000000000001</v>
       </c>
       <c r="S14" s="2">
-        <f t="shared" si="3"/>
-        <v>-2.6440000000000001</v>
+        <f>H14/1000000</f>
+        <v>-3.5817100000000002</v>
       </c>
       <c r="T14" s="2">
         <f t="shared" si="4"/>
-        <v>-3.8310399999999998</v>
+        <v>-3.8365</v>
       </c>
       <c r="U14" s="2">
         <f t="shared" si="5"/>
-        <v>-13.1509</v>
+        <v>-11.035600000000001</v>
       </c>
       <c r="W14" s="3">
         <f t="shared" si="6"/>
@@ -4135,18 +4144,18 @@
       </c>
       <c r="X14" s="3">
         <f t="shared" si="6"/>
-        <v>-3.1929430300000003</v>
+        <v>-5.6273430300000005</v>
       </c>
       <c r="Y14" s="3">
-        <f>Y13+O14</f>
-        <v>-6.2746230299999999</v>
+        <f t="shared" si="7"/>
+        <v>-6.2887930299999999</v>
       </c>
       <c r="Z14" s="3">
-        <f>Z13+P14</f>
-        <v>-30.46973303</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>-24.978333029999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -4154,25 +4163,25 @@
         <v>-131317</v>
       </c>
       <c r="C15" s="1">
-        <v>-131317</v>
+        <v>-1242720</v>
       </c>
       <c r="D15" s="1">
-        <v>-1045060</v>
+        <v>-1051530</v>
       </c>
       <c r="E15" s="1">
-        <v>-12584400</v>
+        <v>-10077300</v>
       </c>
       <c r="G15" s="1">
         <v>-2690380</v>
       </c>
       <c r="H15" s="1">
-        <v>-2690380</v>
+        <v>-4020640</v>
       </c>
       <c r="I15" s="1">
-        <v>-4200150</v>
+        <v>-4207900</v>
       </c>
       <c r="J15" s="1">
-        <v>-17595600</v>
+        <v>-14594800</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -4183,15 +4192,15 @@
       </c>
       <c r="N15" s="2">
         <f t="shared" si="0"/>
-        <v>-0.13131699999999999</v>
+        <v>-1.24272</v>
       </c>
       <c r="O15" s="2">
         <f t="shared" si="1"/>
-        <v>-1.0450600000000001</v>
+        <v>-1.0515300000000001</v>
       </c>
       <c r="P15" s="2">
         <f t="shared" si="2"/>
-        <v>-12.5844</v>
+        <v>-10.077299999999999</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="2">
@@ -4199,35 +4208,35 @@
         <v>-2.6903800000000002</v>
       </c>
       <c r="S15" s="2">
-        <f t="shared" si="3"/>
-        <v>-2.6903800000000002</v>
+        <f>H15/1000000</f>
+        <v>-4.0206400000000002</v>
       </c>
       <c r="T15" s="5">
         <f t="shared" si="4"/>
-        <v>-4.2001499999999998</v>
+        <v>-4.2079000000000004</v>
       </c>
       <c r="U15" s="2">
         <f t="shared" si="5"/>
-        <v>-17.595600000000001</v>
+        <v>-14.594799999999999</v>
       </c>
       <c r="W15" s="3">
-        <f t="shared" ref="W15:X23" si="7">W14+M15</f>
+        <f t="shared" ref="W15:X23" si="9">W14+M15</f>
         <v>-3.3242600300000005</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" si="7"/>
-        <v>-3.3242600300000005</v>
+        <f t="shared" si="9"/>
+        <v>-6.8700630300000007</v>
       </c>
       <c r="Y15" s="3">
-        <f t="shared" ref="Y15:Y23" si="8">Y14+O15</f>
-        <v>-7.3196830300000002</v>
+        <f t="shared" ref="Y15:Y23" si="10">Y14+O15</f>
+        <v>-7.3403230300000004</v>
       </c>
       <c r="Z15" s="4">
         <f>Z14+P15</f>
-        <v>-43.054133030000003</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+        <v>-35.055633029999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -4244,10 +4253,10 @@
         <v>-2358840</v>
       </c>
       <c r="H16" s="1">
-        <v>-2086150</v>
+        <v>-3416410</v>
       </c>
       <c r="J16" s="1">
-        <v>-16707400</v>
+        <v>-13706600</v>
       </c>
       <c r="L16">
         <v>13</v>
@@ -4274,8 +4283,8 @@
         <v>-2.3588399999999998</v>
       </c>
       <c r="S16" s="2">
-        <f t="shared" si="3"/>
-        <v>-2.0861499999999999</v>
+        <f>H16/1000000</f>
+        <v>-3.4164099999999999</v>
       </c>
       <c r="T16" s="2">
         <f t="shared" si="4"/>
@@ -4283,26 +4292,26 @@
       </c>
       <c r="U16" s="2">
         <f t="shared" si="5"/>
-        <v>-16.7074</v>
+        <v>-13.7066</v>
       </c>
       <c r="W16" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-2.3005200300000004</v>
       </c>
       <c r="X16" s="3">
-        <f t="shared" si="7"/>
-        <v>-1.4585200300000005</v>
+        <f t="shared" si="9"/>
+        <v>-5.004323030000001</v>
       </c>
       <c r="Y16" s="3">
-        <f t="shared" si="8"/>
-        <v>-7.3196830300000002</v>
+        <f t="shared" si="10"/>
+        <v>-7.3403230300000004</v>
       </c>
       <c r="Z16" s="3">
-        <f t="shared" ref="Z16:Z23" si="9">Z15+P16</f>
-        <v>-40.31151303</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" ref="Z16:Z23" si="11">Z15+P16</f>
+        <v>-32.313013029999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -4310,7 +4319,7 @@
         <v>948880</v>
       </c>
       <c r="C17" s="1">
-        <v>1799270</v>
+        <v>1799260</v>
       </c>
       <c r="E17" s="1">
         <v>2734160</v>
@@ -4319,10 +4328,10 @@
         <v>-2077070</v>
       </c>
       <c r="H17" s="1">
-        <v>-1551860</v>
+        <v>-2882120</v>
       </c>
       <c r="J17" s="1">
-        <v>-15895500</v>
+        <v>-12894700</v>
       </c>
       <c r="L17">
         <v>14</v>
@@ -4333,7 +4342,7 @@
       </c>
       <c r="N17" s="2">
         <f t="shared" si="0"/>
-        <v>1.7992699999999999</v>
+        <v>1.7992600000000001</v>
       </c>
       <c r="O17" s="2">
         <f t="shared" si="1"/>
@@ -4349,8 +4358,8 @@
         <v>-2.07707</v>
       </c>
       <c r="S17" s="2">
-        <f t="shared" si="3"/>
-        <v>-1.55186</v>
+        <f>H17/1000000</f>
+        <v>-2.88212</v>
       </c>
       <c r="T17" s="2">
         <f t="shared" si="4"/>
@@ -4358,26 +4367,26 @@
       </c>
       <c r="U17" s="2">
         <f t="shared" si="5"/>
-        <v>-15.8955</v>
+        <v>-12.8947</v>
       </c>
       <c r="W17" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-1.3516400300000004</v>
       </c>
       <c r="X17" s="3">
-        <f t="shared" si="7"/>
-        <v>0.3407499699999994</v>
+        <f t="shared" si="9"/>
+        <v>-3.2050630300000007</v>
       </c>
       <c r="Y17" s="3">
-        <f t="shared" si="8"/>
-        <v>-7.3196830300000002</v>
+        <f t="shared" si="10"/>
+        <v>-7.3403230300000004</v>
       </c>
       <c r="Z17" s="3">
-        <f t="shared" si="9"/>
-        <v>-37.577353029999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v>-29.578853029999994</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -4394,10 +4403,10 @@
         <v>-1839550</v>
       </c>
       <c r="H18" s="1">
-        <v>-1080490</v>
+        <v>-2410750</v>
       </c>
       <c r="J18" s="1">
-        <v>-15153500</v>
+        <v>-12152700</v>
       </c>
       <c r="L18">
         <v>15</v>
@@ -4424,8 +4433,8 @@
         <v>-1.83955</v>
       </c>
       <c r="S18" s="2">
-        <f t="shared" si="3"/>
-        <v>-1.08049</v>
+        <f>H18/1000000</f>
+        <v>-2.4107500000000002</v>
       </c>
       <c r="T18" s="2">
         <f t="shared" si="4"/>
@@ -4433,26 +4442,26 @@
       </c>
       <c r="U18" s="2">
         <f t="shared" si="5"/>
-        <v>-15.153499999999999</v>
+        <v>-12.152699999999999</v>
       </c>
       <c r="W18" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-0.47931203000000044</v>
       </c>
       <c r="X18" s="3">
-        <f t="shared" si="7"/>
-        <v>2.0719299699999993</v>
+        <f t="shared" si="9"/>
+        <v>-1.4738830300000008</v>
       </c>
       <c r="Y18" s="3">
-        <f t="shared" si="8"/>
-        <v>-7.3196830300000002</v>
+        <f t="shared" si="10"/>
+        <v>-7.3403230300000004</v>
       </c>
       <c r="Z18" s="3">
-        <f t="shared" si="9"/>
-        <v>-34.852203029999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v>-26.853703029999995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -4469,10 +4478,10 @@
         <v>-1643940</v>
       </c>
       <c r="H19" s="1">
-        <v>-668333</v>
+        <v>-1998590</v>
       </c>
       <c r="J19" s="1">
-        <v>-14478100</v>
+        <v>-11477400</v>
       </c>
       <c r="L19">
         <v>16</v>
@@ -4499,8 +4508,8 @@
         <v>-1.64394</v>
       </c>
       <c r="S19" s="2">
-        <f t="shared" si="3"/>
-        <v>-0.66833299999999995</v>
+        <f>H19/1000000</f>
+        <v>-1.9985900000000001</v>
       </c>
       <c r="T19" s="2">
         <f t="shared" si="4"/>
@@ -4508,26 +4517,26 @@
       </c>
       <c r="U19" s="2">
         <f t="shared" si="5"/>
-        <v>-14.4781</v>
+        <v>-11.477399999999999</v>
       </c>
       <c r="W19" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.3041599699999995</v>
       </c>
       <c r="X19" s="3">
-        <f t="shared" si="7"/>
-        <v>3.7228099699999992</v>
+        <f t="shared" si="9"/>
+        <v>0.17699696999999914</v>
       </c>
       <c r="Y19" s="3">
-        <f t="shared" si="8"/>
-        <v>-7.3196830300000002</v>
+        <f t="shared" si="10"/>
+        <v>-7.3403230300000004</v>
       </c>
       <c r="Z19" s="3">
-        <f t="shared" si="9"/>
-        <v>-32.147223029999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v>-24.148723029999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -4544,10 +4553,10 @@
         <v>-1485340</v>
       </c>
       <c r="H20" s="1">
-        <v>-309185</v>
+        <v>-1639440</v>
       </c>
       <c r="J20" s="1">
-        <v>-13863700</v>
+        <v>-10862900</v>
       </c>
       <c r="L20">
         <v>17</v>
@@ -4574,8 +4583,8 @@
         <v>-1.4853400000000001</v>
       </c>
       <c r="S20" s="2">
-        <f t="shared" si="3"/>
-        <v>-0.30918499999999999</v>
+        <f>H20/1000000</f>
+        <v>-1.63944</v>
       </c>
       <c r="T20" s="2">
         <f t="shared" si="4"/>
@@ -4583,26 +4592,26 @@
       </c>
       <c r="U20" s="2">
         <f t="shared" si="5"/>
-        <v>-13.8637</v>
+        <v>-10.8629</v>
       </c>
       <c r="W20" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.9969879699999995</v>
       </c>
       <c r="X20" s="3">
-        <f t="shared" si="7"/>
-        <v>5.2916799699999988</v>
+        <f t="shared" si="9"/>
+        <v>1.7458669699999991</v>
       </c>
       <c r="Y20" s="3">
-        <f t="shared" si="8"/>
-        <v>-7.3196830300000002</v>
+        <f t="shared" si="10"/>
+        <v>-7.3403230300000004</v>
       </c>
       <c r="Z20" s="3">
-        <f t="shared" si="9"/>
-        <v>-29.463003029999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v>-21.464503029999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -4619,10 +4628,10 @@
         <v>-1357140</v>
       </c>
       <c r="H21" s="1">
-        <v>4734.1499999999996</v>
+        <v>-1325520</v>
       </c>
       <c r="J21" s="1">
-        <v>-13302500</v>
+        <v>-10301800</v>
       </c>
       <c r="L21">
         <v>18</v>
@@ -4649,8 +4658,8 @@
         <v>-1.35714</v>
       </c>
       <c r="S21" s="2">
-        <f t="shared" si="3"/>
-        <v>4.7341499999999995E-3</v>
+        <f>H21/1000000</f>
+        <v>-1.32552</v>
       </c>
       <c r="T21" s="2">
         <f t="shared" si="4"/>
@@ -4658,26 +4667,26 @@
       </c>
       <c r="U21" s="2">
         <f t="shared" si="5"/>
-        <v>-13.3025</v>
+        <v>-10.3018</v>
       </c>
       <c r="W21" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1.6077639699999995</v>
       </c>
       <c r="X21" s="3">
-        <f t="shared" si="7"/>
-        <v>6.7872199699999989</v>
+        <f t="shared" si="9"/>
+        <v>3.241406969999999</v>
       </c>
       <c r="Y21" s="3">
-        <f t="shared" si="8"/>
-        <v>-7.3196830300000002</v>
+        <f t="shared" si="10"/>
+        <v>-7.3403230300000004</v>
       </c>
       <c r="Z21" s="3">
-        <f t="shared" si="9"/>
-        <v>-26.78975303</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v>-18.791253029999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -4694,10 +4703,10 @@
         <v>-1255740</v>
       </c>
       <c r="H22" s="1">
-        <v>278115</v>
+        <v>-1052140</v>
       </c>
       <c r="J22" s="1">
-        <v>-12790300</v>
+        <v>-9789500</v>
       </c>
       <c r="L22">
         <v>19</v>
@@ -4724,8 +4733,8 @@
         <v>-1.2557400000000001</v>
       </c>
       <c r="S22" s="2">
-        <f t="shared" si="3"/>
-        <v>0.278115</v>
+        <f>H22/1000000</f>
+        <v>-1.0521400000000001</v>
       </c>
       <c r="T22" s="2">
         <f t="shared" si="4"/>
@@ -4733,26 +4742,26 @@
       </c>
       <c r="U22" s="2">
         <f t="shared" si="5"/>
-        <v>-12.7903</v>
+        <v>-9.7895000000000003</v>
       </c>
       <c r="W22" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2.1346019699999994</v>
       </c>
       <c r="X22" s="3">
-        <f t="shared" si="7"/>
-        <v>8.2076199699999997</v>
+        <f t="shared" si="9"/>
+        <v>4.6618069699999989</v>
       </c>
       <c r="Y22" s="3">
-        <f t="shared" si="8"/>
-        <v>-7.3196830300000002</v>
+        <f t="shared" si="10"/>
+        <v>-7.3403230300000004</v>
       </c>
       <c r="Z22" s="3">
-        <f t="shared" si="9"/>
-        <v>-24.12815303</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v>-16.129653029999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -4768,11 +4777,11 @@
       <c r="G23" s="1">
         <v>-1177910</v>
       </c>
-      <c r="H23" s="1">
-        <v>515202</v>
+      <c r="H23">
+        <v>-815057</v>
       </c>
       <c r="J23" s="1">
-        <v>-12322700</v>
+        <v>-9321960</v>
       </c>
       <c r="L23">
         <v>20</v>
@@ -4799,8 +4808,8 @@
         <v>-1.17791</v>
       </c>
       <c r="S23" s="2">
-        <f t="shared" si="3"/>
-        <v>0.51520200000000005</v>
+        <f>H23/1000000</f>
+        <v>-0.81505700000000003</v>
       </c>
       <c r="T23" s="2">
         <f t="shared" si="4"/>
@@ -4808,26 +4817,26 @@
       </c>
       <c r="U23" s="2">
         <f t="shared" si="5"/>
-        <v>-12.322699999999999</v>
+        <v>-9.3219600000000007</v>
       </c>
       <c r="W23" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2.5755829699999992</v>
       </c>
       <c r="X23" s="3">
-        <f t="shared" si="7"/>
-        <v>9.551059969999999</v>
+        <f t="shared" si="9"/>
+        <v>6.0052469699999991</v>
       </c>
       <c r="Y23" s="3">
-        <f t="shared" si="8"/>
-        <v>-7.3196830300000002</v>
+        <f t="shared" si="10"/>
+        <v>-7.3403230300000004</v>
       </c>
       <c r="Z23" s="3">
-        <f t="shared" si="9"/>
-        <v>-21.478893030000002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v>-13.480393029999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -4843,11 +4852,11 @@
       <c r="G24" s="1">
         <v>-1121760</v>
       </c>
-      <c r="H24" s="1">
-        <v>718843</v>
+      <c r="H24">
+        <v>-611416</v>
       </c>
       <c r="J24" s="1">
-        <v>-11897100</v>
+        <v>-8896370</v>
       </c>
       <c r="L24">
         <v>21</v>
@@ -4874,8 +4883,8 @@
         <v>-1.1217600000000001</v>
       </c>
       <c r="S24" s="2">
-        <f t="shared" si="3"/>
-        <v>0.71884300000000001</v>
+        <f>H24/1000000</f>
+        <v>-0.61141599999999996</v>
       </c>
       <c r="T24" s="2">
         <f t="shared" si="4"/>
@@ -4883,10 +4892,10 @@
       </c>
       <c r="U24" s="2">
         <f t="shared" si="5"/>
-        <v>-11.8971</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+        <v>-8.8963699999999992</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -4902,11 +4911,11 @@
       <c r="G25" s="1">
         <v>-1084510</v>
       </c>
-      <c r="H25" s="1">
-        <v>892676</v>
+      <c r="H25">
+        <v>-437583</v>
       </c>
       <c r="J25" s="1">
-        <v>-11509900</v>
+        <v>-8509080</v>
       </c>
       <c r="L25">
         <v>22</v>
@@ -4933,8 +4942,8 @@
         <v>-1.0845100000000001</v>
       </c>
       <c r="S25" s="2">
-        <f t="shared" si="3"/>
-        <v>0.89267600000000003</v>
+        <f>H25/1000000</f>
+        <v>-0.437583</v>
       </c>
       <c r="T25" s="2">
         <f t="shared" si="4"/>
@@ -4942,10 +4951,10 @@
       </c>
       <c r="U25" s="2">
         <f t="shared" si="5"/>
-        <v>-11.5099</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+        <v>-8.5090800000000009</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -4961,11 +4970,11 @@
       <c r="G26" s="1">
         <v>-1062840</v>
       </c>
-      <c r="H26" s="1">
-        <v>1040820</v>
+      <c r="H26">
+        <v>-289439</v>
       </c>
       <c r="J26" s="1">
-        <v>-11156700</v>
+        <v>-8155950</v>
       </c>
       <c r="L26">
         <v>23</v>
@@ -4992,8 +5001,8 @@
         <v>-1.06284</v>
       </c>
       <c r="S26" s="5">
-        <f t="shared" si="3"/>
-        <v>1.0408200000000001</v>
+        <f>H26/1000000</f>
+        <v>-0.289439</v>
       </c>
       <c r="T26" s="2">
         <f t="shared" si="4"/>
@@ -5001,10 +5010,10 @@
       </c>
       <c r="U26" s="5">
         <f t="shared" si="5"/>
-        <v>-11.156700000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+        <v>-8.1559500000000007</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -5020,11 +5029,11 @@
       <c r="G27" s="1">
         <v>-1054680</v>
       </c>
-      <c r="H27" s="1">
-        <v>1166100</v>
+      <c r="H27">
+        <v>-164159</v>
       </c>
       <c r="J27" s="1">
-        <v>-10834800</v>
+        <v>-7834050</v>
       </c>
       <c r="L27">
         <v>24</v>
@@ -5051,8 +5060,8 @@
         <v>-1.0546800000000001</v>
       </c>
       <c r="S27" s="2">
-        <f t="shared" si="3"/>
-        <v>1.1660999999999999</v>
+        <f>H27/1000000</f>
+        <v>-0.164159</v>
       </c>
       <c r="T27" s="2">
         <f t="shared" si="4"/>
@@ -5060,10 +5069,10 @@
       </c>
       <c r="U27" s="2">
         <f t="shared" si="5"/>
-        <v>-10.8348</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+        <v>-7.8340500000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -5079,11 +5088,11 @@
       <c r="G28" s="1">
         <v>-980417</v>
       </c>
-      <c r="H28" s="1">
-        <v>1348820</v>
+      <c r="H28">
+        <v>18563.7</v>
       </c>
       <c r="J28" s="1">
-        <v>-10463700</v>
+        <v>-7462960</v>
       </c>
       <c r="L28">
         <v>25</v>
@@ -5110,8 +5119,8 @@
         <v>-0.98041699999999998</v>
       </c>
       <c r="S28" s="2">
-        <f t="shared" si="3"/>
-        <v>1.3488199999999999</v>
+        <f>H28/1000000</f>
+        <v>1.8563700000000002E-2</v>
       </c>
       <c r="T28" s="2">
         <f t="shared" si="4"/>
@@ -5119,8 +5128,341 @@
       </c>
       <c r="U28" s="2">
         <f t="shared" si="5"/>
-        <v>-10.463699999999999</v>
-      </c>
+        <v>-7.4629599999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J33" t="s">
+        <v>11</v>
+      </c>
+      <c r="K33" t="s">
+        <v>13</v>
+      </c>
+      <c r="L33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1">
+        <v>-13557300</v>
+      </c>
+      <c r="L34" s="1">
+        <v>-13557300</v>
+      </c>
+    </row>
+    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J35">
+        <v>2</v>
+      </c>
+      <c r="K35" s="1">
+        <v>-4423200</v>
+      </c>
+      <c r="L35" s="1">
+        <v>9961670</v>
+      </c>
+    </row>
+    <row r="36" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J36">
+        <v>3</v>
+      </c>
+      <c r="K36" s="1">
+        <v>-2528160</v>
+      </c>
+      <c r="L36" s="1">
+        <v>2253980</v>
+      </c>
+    </row>
+    <row r="37" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J37">
+        <v>4</v>
+      </c>
+      <c r="K37" s="1">
+        <v>-1520630</v>
+      </c>
+      <c r="L37" s="1">
+        <v>1306930</v>
+      </c>
+    </row>
+    <row r="38" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J38">
+        <v>5</v>
+      </c>
+      <c r="K38" s="1">
+        <v>-1042570</v>
+      </c>
+      <c r="L38" s="1">
+        <v>676313</v>
+      </c>
+    </row>
+    <row r="39" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J39">
+        <v>6</v>
+      </c>
+      <c r="K39" s="1">
+        <v>-703987</v>
+      </c>
+      <c r="L39" s="1">
+        <v>522382</v>
+      </c>
+    </row>
+    <row r="40" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J40">
+        <v>7</v>
+      </c>
+      <c r="K40" s="1">
+        <v>-702556</v>
+      </c>
+      <c r="L40" s="1">
+        <v>2407.9699999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J41">
+        <v>8</v>
+      </c>
+      <c r="K41">
+        <v>-987222</v>
+      </c>
+      <c r="L41" s="1">
+        <v>-522389</v>
+      </c>
+    </row>
+    <row r="42" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J42">
+        <v>9</v>
+      </c>
+      <c r="K42" s="1">
+        <v>-1332610</v>
+      </c>
+      <c r="L42" s="1">
+        <v>-691240</v>
+      </c>
+    </row>
+    <row r="43" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J43">
+        <v>10</v>
+      </c>
+      <c r="K43" s="1">
+        <v>-1729280</v>
+      </c>
+      <c r="L43" s="1">
+        <v>-865807</v>
+      </c>
+    </row>
+    <row r="44" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J44" s="1">
+        <v>11</v>
+      </c>
+      <c r="K44" s="1">
+        <v>-2168900</v>
+      </c>
+      <c r="L44" s="1">
+        <v>-1046480</v>
+      </c>
+    </row>
+    <row r="45" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J45" s="1">
+        <v>12</v>
+      </c>
+      <c r="K45" s="1">
+        <v>-11035600</v>
+      </c>
+      <c r="L45" s="1">
+        <v>-23018800</v>
+      </c>
+    </row>
+    <row r="46" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J46" s="1">
+        <v>13</v>
+      </c>
+      <c r="K46" s="1">
+        <v>-14594800</v>
+      </c>
+      <c r="L46" s="1">
+        <v>-10077300</v>
+      </c>
+    </row>
+    <row r="47" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J47" s="1">
+        <v>14</v>
+      </c>
+      <c r="K47" s="1">
+        <v>-13706600</v>
+      </c>
+      <c r="L47" s="1">
+        <v>2742620</v>
+      </c>
+    </row>
+    <row r="48" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J48">
+        <v>15</v>
+      </c>
+      <c r="K48" s="1">
+        <v>-12894700</v>
+      </c>
+      <c r="L48" s="1">
+        <v>2734160</v>
+      </c>
+    </row>
+    <row r="49" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J49">
+        <v>16</v>
+      </c>
+      <c r="K49" s="1">
+        <v>-12152700</v>
+      </c>
+      <c r="L49" s="1">
+        <v>2725150</v>
+      </c>
+    </row>
+    <row r="50" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J50">
+        <v>17</v>
+      </c>
+      <c r="K50" s="1">
+        <v>-11477400</v>
+      </c>
+      <c r="L50" s="1">
+        <v>2704980</v>
+      </c>
+    </row>
+    <row r="51" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J51">
+        <v>18</v>
+      </c>
+      <c r="K51" s="1">
+        <v>-10862900</v>
+      </c>
+      <c r="L51" s="1">
+        <v>2684220</v>
+      </c>
+    </row>
+    <row r="52" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J52">
+        <v>19</v>
+      </c>
+      <c r="K52" s="1">
+        <v>-10301800</v>
+      </c>
+      <c r="L52" s="1">
+        <v>2673250</v>
+      </c>
+    </row>
+    <row r="53" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J53">
+        <v>20</v>
+      </c>
+      <c r="K53" s="1">
+        <v>-9789500</v>
+      </c>
+      <c r="L53" s="1">
+        <v>2661600</v>
+      </c>
+    </row>
+    <row r="54" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J54" s="1">
+        <v>21</v>
+      </c>
+      <c r="K54" s="1">
+        <v>-9321960</v>
+      </c>
+      <c r="L54" s="1">
+        <v>2649260</v>
+      </c>
+    </row>
+    <row r="55" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J55" s="1">
+        <v>22</v>
+      </c>
+      <c r="K55" s="1">
+        <v>-8896370</v>
+      </c>
+      <c r="L55" s="1">
+        <v>2630080</v>
+      </c>
+    </row>
+    <row r="56" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J56">
+        <v>23</v>
+      </c>
+      <c r="K56" s="1">
+        <v>-8509080</v>
+      </c>
+      <c r="L56" s="1">
+        <v>2610170</v>
+      </c>
+    </row>
+    <row r="57" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J57" s="1">
+        <v>24</v>
+      </c>
+      <c r="K57" s="1">
+        <v>-8155950</v>
+      </c>
+      <c r="L57" s="1">
+        <v>2595680</v>
+      </c>
+    </row>
+    <row r="58" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J58" s="1">
+        <v>25</v>
+      </c>
+      <c r="K58" s="1">
+        <v>-7834050</v>
+      </c>
+      <c r="L58" s="1">
+        <v>2580430</v>
+      </c>
+    </row>
+    <row r="59" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J59" s="1">
+        <v>26</v>
+      </c>
+      <c r="K59" s="1">
+        <v>-7462960</v>
+      </c>
+      <c r="L59" s="1">
+        <v>3244240</v>
+      </c>
+    </row>
+    <row r="60" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+    </row>
+    <row r="61" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+    </row>
+    <row r="62" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+    </row>
+    <row r="63" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J63" s="1"/>
+    </row>
+    <row r="64" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J64" s="1"/>
+    </row>
+    <row r="65" spans="10:11" x14ac:dyDescent="0.25">
+      <c r="J65" s="1"/>
+    </row>
+    <row r="66" spans="10:11" x14ac:dyDescent="0.25">
+      <c r="J66" s="1"/>
+    </row>
+    <row r="67" spans="10:11" x14ac:dyDescent="0.25">
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+    </row>
+    <row r="68" spans="10:11" x14ac:dyDescent="0.25">
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+    </row>
+    <row r="69" spans="10:11" x14ac:dyDescent="0.25">
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5140,6 +5482,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A788E4FEB44D0B4CB1AD2E9A3A83F076" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1d34d9b8e131c103df8a093e310b027">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8baa01ab-7cf8-4360-9f3f-f87b1ec95c26" xmlns:ns3="d481fc2a-e230-47f7-a716-4f7f4b27a8e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c44e149c0724d485dcb6f09127e30ffd" ns2:_="" ns3:_="">
     <xsd:import namespace="8baa01ab-7cf8-4360-9f3f-f87b1ec95c26"/>
@@ -5368,15 +5719,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A82D478-F143-4E1A-BE03-DF93E0476218}">
   <ds:schemaRefs>
@@ -5389,6 +5731,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB2C9E99-917F-4BDF-B9E4-ADA5D0AFF133}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F33A64FD-BD8E-4A10-881A-543F22FB0B66}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5407,14 +5757,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB2C9E99-917F-4BDF-B9E4-ADA5D0AFF133}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{95965d95-ecc0-4720-b759-1f33c42ed7da}" enabled="1" method="Standard" siteId="{a0f29d7e-28cd-4f54-8442-7885aee7c080}" removed="0"/>

--- a/Studies/Journal - Simon Solar captest/plots/2026-08-EPRI_scenarios_SAMresults.xlsx
+++ b/Studies/Journal - Simon Solar captest/plots/2026-08-EPRI_scenarios_SAMresults.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmirletz\source\repos\pv_repowering\Studies\Journal - Simon Solar captest\plots\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdeline\Documents\Python Scripts\pv_repowering\Studies\Journal - Simon Solar captest\plots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93E59ED-9593-4DCF-A4C4-3CC3F4AFB89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F279AB-2BCB-40C1-AC30-198F6F57735C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{04F1D575-AB74-4BA9-9193-B5993F01A15B}"/>
+    <workbookView xWindow="-28920" yWindow="-6360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{04F1D575-AB74-4BA9-9193-B5993F01A15B}"/>
   </bookViews>
   <sheets>
     <sheet name="Simon" sheetId="2" r:id="rId1"/>
+    <sheet name="Simon_cdeline" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="18">
   <si>
     <t>Year</t>
   </si>
@@ -79,6 +80,18 @@
   <si>
     <t>After-tax cumulative NPV | ($)</t>
   </si>
+  <si>
+    <t>Crappy</t>
+  </si>
+  <si>
+    <t>Median degradation</t>
+  </si>
+  <si>
+    <t>Repowered degradation</t>
+  </si>
+  <si>
+    <t>&lt;- Repair / repower action</t>
+  </si>
 </sst>
 </file>
 
@@ -87,8 +100,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -128,13 +149,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1590,6 +1613,1445 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1920" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Annual Cashflow ($M)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1920" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.17886167843477394"/>
+          <c:y val="0.17171296296296296"/>
+          <c:w val="0.80621175365127551"/>
+          <c:h val="0.6714577865266842"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Simon_cdeline!$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Do Nothing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Simon_cdeline!$M$3:$M$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>-13.5573</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9616699999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.3631099999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5274399999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.99451400000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.94018500000000005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.51851700000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.50978E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.62171200000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.94605799999999995</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1.1275200000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1.3152600000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.213974</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.94026399999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.86457099999999998</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.78717800000000004</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.69747400000000004</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.60597199999999996</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.52305599999999997</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.43824800000000003</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.35151199999999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.25666800000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.159832</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.711389999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9F37-4CDA-8924-42A83DDC2F0B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Simon_cdeline!$O$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Decommission</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Simon_cdeline!$O$3:$O$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>-13.5573</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9616699999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.3631099999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5274399999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.99451400000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.94018500000000005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.51851700000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.50978E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.62171200000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.94605799999999995</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1.1275200000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-4.4111099999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1.13419</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9F37-4CDA-8924-42A83DDC2F0B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Simon_cdeline!$P$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Repower</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Simon_cdeline!$P$3:$P$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>-13.5573</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9616699999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.3631099999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5274399999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.99451400000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.94018500000000005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.51851700000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.50978E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.62171200000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.94605799999999995</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1.1275200000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-23.1006</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-10.1599</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.7426200000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.7341600000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.7251500000000002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.7049799999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.6842199999999998</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.6732499999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.6616</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.6492599999999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.63008</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.6101700000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.5956800000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9F37-4CDA-8924-42A83DDC2F0B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Simon_cdeline!$N$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Repair</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Simon_cdeline!$N$3:$N$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>-13.5573</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9616699999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.3631099999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5274399999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.99451400000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.94018500000000005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.51851700000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.50978E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.62171200000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.94605799999999995</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1.1275200000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-3.74966</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1.32538</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.6360699999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.56731</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.49691</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.4142699999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.3299000000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.2541899999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.17665</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.0972599999999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.0098400000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.92048399999999997</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.835318</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-9F37-4CDA-8924-42A83DDC2F0B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="937552936"/>
+        <c:axId val="937551856"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="937552936"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="937551856"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="0"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="937551856"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="-25"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="937552936"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1600">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1920" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1920" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Cumulative Net Present Value ($M)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1920" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.17381809163618331"/>
+          <c:y val="0.20098977073753074"/>
+          <c:w val="0.80308479550292422"/>
+          <c:h val="0.60270547615703174"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Simon_cdeline!$R$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Do Nothing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Simon_cdeline!$R$3:$R$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>-13.5573</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.4231999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-2.43641</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.2588900000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.555898</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.3478699999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.36163400000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.37531100000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.4664899999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.36877399999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.84243900000000005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1.34907</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1.4246399999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1.1201300000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.86339999999999995</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.64906600000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.47493299999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.33621299999999998</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.22642200000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.14207400000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-8.0039699999999991E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-3.8506400000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-1.4791500000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-5.6607200000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-9.1125700000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5.4402900000000004E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5074-4CB0-B026-415EB6DEC3A7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Simon_cdeline!$T$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Decommission</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Simon_cdeline!$T$3:$T$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>-13.5573</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.4231999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-2.43641</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.2588900000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.555898</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.3478699999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.36163400000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.37531100000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.4664899999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.36877399999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.84243900000000005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-2.5415700000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-2.9421599999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5074-4CB0-B026-415EB6DEC3A7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Simon_cdeline!$U$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Repower</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Simon_cdeline!$U$3:$U$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>-13.5573</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.4231999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-2.43641</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.2588900000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.555898</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.3478699999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.36163400000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.37531100000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.4664899999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.36877399999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.84243900000000005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-9.7406500000000005</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-13.3291</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-12.440899999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-11.629</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-10.887</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-10.211600000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-9.5971499999999992</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-9.0360300000000002</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-8.5237599999999993</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-8.0562199999999997</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-7.63063</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-7.2433500000000004</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-6.8902099999999997</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-6.5683100000000003</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-6.1972199999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5074-4CB0-B026-415EB6DEC3A7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Simon_cdeline!$S$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Repair</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Simon_cdeline!$S$3:$S$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>-13.5573</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.4231999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-2.43641</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.2588900000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.555898</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.3478699999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.36163400000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.37531100000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.4664899999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.36877399999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.84243900000000005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-2.2867799999999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-2.7549000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-2.22505</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-1.7596400000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-1.35206</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.998973</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.69453100000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.43127100000000002</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.20480499999999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-1.1162E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.15224699999999999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.288823</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.40246700000000002</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.49579600000000001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.64893299999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-5074-4CB0-B026-415EB6DEC3A7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="924469128"/>
+        <c:axId val="924467688"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="924469128"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="924467688"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="924467688"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="924469128"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1631,6 +3093,86 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2689,6 +4231,1025 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -2752,6 +5313,87 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>130176</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>96837</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E50A8690-51AE-4F2F-9D06-5FDA9D67B177}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>194309</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>131761</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>149859</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C62A5EFA-1953-4A71-BC80-40A7AE25646E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -3085,20 +5727,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A66F2B7E-C15E-4BE7-BAE2-4B1EBEE71C1F}">
-  <dimension ref="A1:Z69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Z80"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.7265625" customWidth="1"/>
     <col min="7" max="8" width="13" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.7265625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9" customWidth="1"/>
-    <col min="17" max="17" width="3.28515625" customWidth="1"/>
-    <col min="22" max="22" width="2.7109375" customWidth="1"/>
+    <col min="17" max="17" width="3.26953125" customWidth="1"/>
+    <col min="22" max="22" width="2.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -3115,7 +5757,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3183,7 +5825,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>0</v>
       </c>
@@ -3264,7 +5906,7 @@
         <v>-13.5573</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3317,15 +5959,15 @@
         <v>-4.4231999999999996</v>
       </c>
       <c r="S4" s="2">
-        <f>H4/1000000</f>
+        <f t="shared" ref="S4:S28" si="4">H4/1000000</f>
         <v>-4.4231999999999996</v>
       </c>
       <c r="T4" s="2">
-        <f t="shared" ref="T4:T28" si="4">I4/1000000</f>
+        <f t="shared" ref="T4:T28" si="5">I4/1000000</f>
         <v>-4.4231999999999996</v>
       </c>
       <c r="U4" s="2">
-        <f t="shared" ref="U4:U28" si="5">J4/1000000</f>
+        <f t="shared" ref="U4:U28" si="6">J4/1000000</f>
         <v>-4.4231999999999996</v>
       </c>
       <c r="W4" s="3">
@@ -3345,7 +5987,7 @@
         <v>-3.5956299999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -3398,35 +6040,35 @@
         <v>-2.5281600000000002</v>
       </c>
       <c r="S5" s="2">
-        <f>H5/1000000</f>
-        <v>-2.5281600000000002</v>
-      </c>
-      <c r="T5" s="2">
         <f t="shared" si="4"/>
         <v>-2.5281600000000002</v>
       </c>
-      <c r="U5" s="2">
+      <c r="T5" s="2">
         <f t="shared" si="5"/>
         <v>-2.5281600000000002</v>
       </c>
+      <c r="U5" s="2">
+        <f t="shared" si="6"/>
+        <v>-2.5281600000000002</v>
+      </c>
       <c r="W5" s="3">
-        <f t="shared" ref="W5:X14" si="6">W4+M5</f>
+        <f t="shared" ref="W5:X14" si="7">W4+M5</f>
         <v>-1.34165</v>
       </c>
       <c r="X5" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.34165</v>
       </c>
       <c r="Y5" s="3">
-        <f t="shared" ref="Y5:Y14" si="7">Y4+O5</f>
+        <f t="shared" ref="Y5:Y14" si="8">Y4+O5</f>
         <v>-1.34165</v>
       </c>
       <c r="Z5" s="3">
-        <f t="shared" ref="Z5:Z14" si="8">Z4+P5</f>
+        <f t="shared" ref="Z5:Z14" si="9">Z4+P5</f>
         <v>-1.34165</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -3479,35 +6121,35 @@
         <v>-1.5206299999999999</v>
       </c>
       <c r="S6" s="2">
-        <f>H6/1000000</f>
-        <v>-1.5206299999999999</v>
-      </c>
-      <c r="T6" s="2">
         <f t="shared" si="4"/>
         <v>-1.5206299999999999</v>
       </c>
-      <c r="U6" s="2">
+      <c r="T6" s="2">
         <f t="shared" si="5"/>
         <v>-1.5206299999999999</v>
       </c>
+      <c r="U6" s="2">
+        <f t="shared" si="6"/>
+        <v>-1.5206299999999999</v>
+      </c>
       <c r="W6" s="3">
-        <f t="shared" si="6"/>
-        <v>-3.4720000000000084E-2</v>
-      </c>
-      <c r="X6" s="3">
-        <f t="shared" si="6"/>
-        <v>-3.4720000000000084E-2</v>
-      </c>
-      <c r="Y6" s="3">
         <f t="shared" si="7"/>
         <v>-3.4720000000000084E-2</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="X6" s="3">
+        <f t="shared" si="7"/>
+        <v>-3.4720000000000084E-2</v>
+      </c>
+      <c r="Y6" s="3">
         <f t="shared" si="8"/>
         <v>-3.4720000000000084E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z6" s="3">
+        <f t="shared" si="9"/>
+        <v>-3.4720000000000084E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4</v>
       </c>
@@ -3560,35 +6202,35 @@
         <v>-1.04257</v>
       </c>
       <c r="S7" s="2">
-        <f>H7/1000000</f>
-        <v>-1.04257</v>
-      </c>
-      <c r="T7" s="2">
         <f t="shared" si="4"/>
         <v>-1.04257</v>
       </c>
-      <c r="U7" s="2">
+      <c r="T7" s="2">
         <f t="shared" si="5"/>
         <v>-1.04257</v>
       </c>
+      <c r="U7" s="2">
+        <f t="shared" si="6"/>
+        <v>-1.04257</v>
+      </c>
       <c r="W7" s="3">
-        <f t="shared" si="6"/>
-        <v>0.64159299999999997</v>
-      </c>
-      <c r="X7" s="3">
-        <f t="shared" si="6"/>
-        <v>0.64159299999999997</v>
-      </c>
-      <c r="Y7" s="3">
         <f t="shared" si="7"/>
         <v>0.64159299999999997</v>
       </c>
-      <c r="Z7" s="3">
+      <c r="X7" s="3">
+        <f t="shared" si="7"/>
+        <v>0.64159299999999997</v>
+      </c>
+      <c r="Y7" s="3">
         <f t="shared" si="8"/>
         <v>0.64159299999999997</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z7" s="3">
+        <f t="shared" si="9"/>
+        <v>0.64159299999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>5</v>
       </c>
@@ -3641,35 +6283,35 @@
         <v>-0.70398700000000003</v>
       </c>
       <c r="S8" s="2">
-        <f>H8/1000000</f>
-        <v>-0.70398700000000003</v>
-      </c>
-      <c r="T8" s="2">
         <f t="shared" si="4"/>
         <v>-0.70398700000000003</v>
       </c>
-      <c r="U8" s="2">
+      <c r="T8" s="2">
         <f t="shared" si="5"/>
         <v>-0.70398700000000003</v>
       </c>
+      <c r="U8" s="2">
+        <f t="shared" si="6"/>
+        <v>-0.70398700000000003</v>
+      </c>
       <c r="W8" s="3">
-        <f t="shared" si="6"/>
-        <v>1.163975</v>
-      </c>
-      <c r="X8" s="3">
-        <f t="shared" si="6"/>
-        <v>1.163975</v>
-      </c>
-      <c r="Y8" s="3">
         <f t="shared" si="7"/>
         <v>1.163975</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="X8" s="3">
+        <f t="shared" si="7"/>
+        <v>1.163975</v>
+      </c>
+      <c r="Y8" s="3">
         <f t="shared" si="8"/>
         <v>1.163975</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z8" s="3">
+        <f t="shared" si="9"/>
+        <v>1.163975</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>6</v>
       </c>
@@ -3722,35 +6364,35 @@
         <v>-0.70255599999999996</v>
       </c>
       <c r="S9" s="2">
-        <f>H9/1000000</f>
-        <v>-0.70255599999999996</v>
-      </c>
-      <c r="T9" s="2">
         <f t="shared" si="4"/>
         <v>-0.70255599999999996</v>
       </c>
-      <c r="U9" s="2">
+      <c r="T9" s="2">
         <f t="shared" si="5"/>
         <v>-0.70255599999999996</v>
       </c>
+      <c r="U9" s="2">
+        <f t="shared" si="6"/>
+        <v>-0.70255599999999996</v>
+      </c>
       <c r="W9" s="3">
-        <f t="shared" si="6"/>
-        <v>1.1663829699999999</v>
-      </c>
-      <c r="X9" s="3">
-        <f t="shared" si="6"/>
-        <v>1.1663829699999999</v>
-      </c>
-      <c r="Y9" s="3">
         <f t="shared" si="7"/>
         <v>1.1663829699999999</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="X9" s="3">
+        <f t="shared" si="7"/>
+        <v>1.1663829699999999</v>
+      </c>
+      <c r="Y9" s="3">
         <f t="shared" si="8"/>
         <v>1.1663829699999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z9" s="3">
+        <f t="shared" si="9"/>
+        <v>1.1663829699999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>7</v>
       </c>
@@ -3803,35 +6445,35 @@
         <v>-0.98722200000000004</v>
       </c>
       <c r="S10" s="2">
-        <f>H10/1000000</f>
-        <v>-0.98722200000000004</v>
-      </c>
-      <c r="T10" s="2">
         <f t="shared" si="4"/>
         <v>-0.98722200000000004</v>
       </c>
-      <c r="U10" s="2">
+      <c r="T10" s="2">
         <f t="shared" si="5"/>
         <v>-0.98722200000000004</v>
       </c>
+      <c r="U10" s="2">
+        <f t="shared" si="6"/>
+        <v>-0.98722200000000004</v>
+      </c>
       <c r="W10" s="3">
-        <f t="shared" si="6"/>
-        <v>0.64399396999999992</v>
-      </c>
-      <c r="X10" s="3">
-        <f t="shared" si="6"/>
-        <v>0.64399396999999992</v>
-      </c>
-      <c r="Y10" s="3">
         <f t="shared" si="7"/>
         <v>0.64399396999999992</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="X10" s="3">
+        <f t="shared" si="7"/>
+        <v>0.64399396999999992</v>
+      </c>
+      <c r="Y10" s="3">
         <f t="shared" si="8"/>
         <v>0.64399396999999992</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z10" s="3">
+        <f t="shared" si="9"/>
+        <v>0.64399396999999992</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>8</v>
       </c>
@@ -3884,35 +6526,35 @@
         <v>-1.3326100000000001</v>
       </c>
       <c r="S11" s="2">
-        <f>H11/1000000</f>
-        <v>-1.3326100000000001</v>
-      </c>
-      <c r="T11" s="2">
         <f t="shared" si="4"/>
         <v>-1.3326100000000001</v>
       </c>
-      <c r="U11" s="2">
+      <c r="T11" s="2">
         <f t="shared" si="5"/>
         <v>-1.3326100000000001</v>
       </c>
+      <c r="U11" s="2">
+        <f t="shared" si="6"/>
+        <v>-1.3326100000000001</v>
+      </c>
       <c r="W11" s="3">
-        <f t="shared" si="6"/>
-        <v>-4.724603000000005E-2</v>
-      </c>
-      <c r="X11" s="3">
-        <f t="shared" si="6"/>
-        <v>-4.724603000000005E-2</v>
-      </c>
-      <c r="Y11" s="3">
         <f t="shared" si="7"/>
         <v>-4.724603000000005E-2</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="X11" s="3">
+        <f t="shared" si="7"/>
+        <v>-4.724603000000005E-2</v>
+      </c>
+      <c r="Y11" s="3">
         <f t="shared" si="8"/>
         <v>-4.724603000000005E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z11" s="3">
+        <f t="shared" si="9"/>
+        <v>-4.724603000000005E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>9</v>
       </c>
@@ -3965,35 +6607,35 @@
         <v>-1.7292799999999999</v>
       </c>
       <c r="S12" s="2">
-        <f>H12/1000000</f>
-        <v>-1.7292799999999999</v>
-      </c>
-      <c r="T12" s="2">
         <f t="shared" si="4"/>
         <v>-1.7292799999999999</v>
       </c>
-      <c r="U12" s="2">
+      <c r="T12" s="2">
         <f t="shared" si="5"/>
         <v>-1.7292799999999999</v>
       </c>
+      <c r="U12" s="2">
+        <f t="shared" si="6"/>
+        <v>-1.7292799999999999</v>
+      </c>
       <c r="W12" s="3">
-        <f t="shared" si="6"/>
-        <v>-0.91305303000000004</v>
-      </c>
-      <c r="X12" s="3">
-        <f t="shared" si="6"/>
-        <v>-0.91305303000000004</v>
-      </c>
-      <c r="Y12" s="3">
         <f t="shared" si="7"/>
         <v>-0.91305303000000004</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="X12" s="3">
+        <f t="shared" si="7"/>
+        <v>-0.91305303000000004</v>
+      </c>
+      <c r="Y12" s="3">
         <f t="shared" si="8"/>
         <v>-0.91305303000000004</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z12" s="3">
+        <f t="shared" si="9"/>
+        <v>-0.91305303000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>10</v>
       </c>
@@ -4046,35 +6688,35 @@
         <v>-2.1688999999999998</v>
       </c>
       <c r="S13" s="2">
-        <f>H13/1000000</f>
-        <v>-2.1688999999999998</v>
-      </c>
-      <c r="T13" s="2">
         <f t="shared" si="4"/>
         <v>-2.1688999999999998</v>
       </c>
-      <c r="U13" s="2">
+      <c r="T13" s="2">
         <f t="shared" si="5"/>
         <v>-2.1688999999999998</v>
       </c>
+      <c r="U13" s="2">
+        <f t="shared" si="6"/>
+        <v>-2.1688999999999998</v>
+      </c>
       <c r="W13" s="3">
-        <f t="shared" si="6"/>
-        <v>-1.9595330300000002</v>
-      </c>
-      <c r="X13" s="3">
-        <f t="shared" si="6"/>
-        <v>-1.9595330300000002</v>
-      </c>
-      <c r="Y13" s="3">
         <f t="shared" si="7"/>
         <v>-1.9595330300000002</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="X13" s="3">
+        <f t="shared" si="7"/>
+        <v>-1.9595330300000002</v>
+      </c>
+      <c r="Y13" s="3">
         <f t="shared" si="8"/>
         <v>-1.9595330300000002</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z13" s="3">
+        <f t="shared" si="9"/>
+        <v>-1.9595330300000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>11</v>
       </c>
@@ -4127,35 +6769,35 @@
         <v>-2.6440000000000001</v>
       </c>
       <c r="S14" s="2">
-        <f>H14/1000000</f>
+        <f t="shared" si="4"/>
         <v>-3.5817100000000002</v>
       </c>
       <c r="T14" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-3.8365</v>
       </c>
       <c r="U14" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-11.035600000000001</v>
       </c>
       <c r="W14" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-3.1929430300000003</v>
       </c>
       <c r="X14" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-5.6273430300000005</v>
       </c>
       <c r="Y14" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-6.2887930299999999</v>
       </c>
       <c r="Z14" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-24.978333029999998</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>12</v>
       </c>
@@ -4208,27 +6850,27 @@
         <v>-2.6903800000000002</v>
       </c>
       <c r="S15" s="2">
-        <f>H15/1000000</f>
+        <f t="shared" si="4"/>
         <v>-4.0206400000000002</v>
       </c>
       <c r="T15" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-4.2079000000000004</v>
       </c>
       <c r="U15" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-14.594799999999999</v>
       </c>
       <c r="W15" s="3">
-        <f t="shared" ref="W15:X23" si="9">W14+M15</f>
+        <f t="shared" ref="W15:X23" si="10">W14+M15</f>
         <v>-3.3242600300000005</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-6.8700630300000007</v>
       </c>
       <c r="Y15" s="3">
-        <f t="shared" ref="Y15:Y23" si="10">Y14+O15</f>
+        <f t="shared" ref="Y15:Y23" si="11">Y14+O15</f>
         <v>-7.3403230300000004</v>
       </c>
       <c r="Z15" s="4">
@@ -4236,7 +6878,7 @@
         <v>-35.055633029999996</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>13</v>
       </c>
@@ -4283,35 +6925,35 @@
         <v>-2.3588399999999998</v>
       </c>
       <c r="S16" s="2">
-        <f>H16/1000000</f>
+        <f t="shared" si="4"/>
         <v>-3.4164099999999999</v>
       </c>
       <c r="T16" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U16" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-13.7066</v>
       </c>
       <c r="W16" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-2.3005200300000004</v>
       </c>
       <c r="X16" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-5.004323030000001</v>
       </c>
       <c r="Y16" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-7.3403230300000004</v>
       </c>
       <c r="Z16" s="3">
-        <f t="shared" ref="Z16:Z23" si="11">Z15+P16</f>
+        <f t="shared" ref="Z16:Z23" si="12">Z15+P16</f>
         <v>-32.313013029999993</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>14</v>
       </c>
@@ -4358,35 +7000,35 @@
         <v>-2.07707</v>
       </c>
       <c r="S17" s="2">
-        <f>H17/1000000</f>
+        <f t="shared" si="4"/>
         <v>-2.88212</v>
       </c>
       <c r="T17" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U17" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-12.8947</v>
       </c>
       <c r="W17" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-1.3516400300000004</v>
       </c>
       <c r="X17" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-3.2050630300000007</v>
       </c>
       <c r="Y17" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-7.3403230300000004</v>
       </c>
       <c r="Z17" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-29.578853029999994</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>15</v>
       </c>
@@ -4433,35 +7075,35 @@
         <v>-1.83955</v>
       </c>
       <c r="S18" s="2">
-        <f>H18/1000000</f>
+        <f t="shared" si="4"/>
         <v>-2.4107500000000002</v>
       </c>
       <c r="T18" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U18" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-12.152699999999999</v>
       </c>
       <c r="W18" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-0.47931203000000044</v>
       </c>
       <c r="X18" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-1.4738830300000008</v>
       </c>
       <c r="Y18" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-7.3403230300000004</v>
       </c>
       <c r="Z18" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-26.853703029999995</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16</v>
       </c>
@@ -4508,35 +7150,35 @@
         <v>-1.64394</v>
       </c>
       <c r="S19" s="2">
-        <f>H19/1000000</f>
+        <f t="shared" si="4"/>
         <v>-1.9985900000000001</v>
       </c>
       <c r="T19" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U19" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-11.477399999999999</v>
       </c>
       <c r="W19" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.3041599699999995</v>
       </c>
       <c r="X19" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.17699696999999914</v>
       </c>
       <c r="Y19" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-7.3403230300000004</v>
       </c>
       <c r="Z19" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-24.148723029999996</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>17</v>
       </c>
@@ -4583,35 +7225,35 @@
         <v>-1.4853400000000001</v>
       </c>
       <c r="S20" s="2">
-        <f>H20/1000000</f>
+        <f t="shared" si="4"/>
         <v>-1.63944</v>
       </c>
       <c r="T20" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U20" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-10.8629</v>
       </c>
       <c r="W20" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.9969879699999995</v>
       </c>
       <c r="X20" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.7458669699999991</v>
       </c>
       <c r="Y20" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-7.3403230300000004</v>
       </c>
       <c r="Z20" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-21.464503029999996</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>18</v>
       </c>
@@ -4658,35 +7300,35 @@
         <v>-1.35714</v>
       </c>
       <c r="S21" s="2">
-        <f>H21/1000000</f>
+        <f t="shared" si="4"/>
         <v>-1.32552</v>
       </c>
       <c r="T21" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U21" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-10.3018</v>
       </c>
       <c r="W21" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.6077639699999995</v>
       </c>
       <c r="X21" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.241406969999999</v>
       </c>
       <c r="Y21" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-7.3403230300000004</v>
       </c>
       <c r="Z21" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-18.791253029999996</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>19</v>
       </c>
@@ -4733,35 +7375,35 @@
         <v>-1.2557400000000001</v>
       </c>
       <c r="S22" s="2">
-        <f>H22/1000000</f>
+        <f t="shared" si="4"/>
         <v>-1.0521400000000001</v>
       </c>
       <c r="T22" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U22" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-9.7895000000000003</v>
       </c>
       <c r="W22" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.1346019699999994</v>
       </c>
       <c r="X22" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.6618069699999989</v>
       </c>
       <c r="Y22" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-7.3403230300000004</v>
       </c>
       <c r="Z22" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-16.129653029999997</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>20</v>
       </c>
@@ -4808,35 +7450,35 @@
         <v>-1.17791</v>
       </c>
       <c r="S23" s="2">
-        <f>H23/1000000</f>
+        <f t="shared" si="4"/>
         <v>-0.81505700000000003</v>
       </c>
       <c r="T23" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U23" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-9.3219600000000007</v>
       </c>
       <c r="W23" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.5755829699999992</v>
       </c>
       <c r="X23" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.0052469699999991</v>
       </c>
       <c r="Y23" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-7.3403230300000004</v>
       </c>
       <c r="Z23" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-13.480393029999997</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>21</v>
       </c>
@@ -4883,19 +7525,19 @@
         <v>-1.1217600000000001</v>
       </c>
       <c r="S24" s="2">
-        <f>H24/1000000</f>
+        <f t="shared" si="4"/>
         <v>-0.61141599999999996</v>
       </c>
       <c r="T24" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U24" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-8.8963699999999992</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>22</v>
       </c>
@@ -4942,19 +7584,19 @@
         <v>-1.0845100000000001</v>
       </c>
       <c r="S25" s="2">
-        <f>H25/1000000</f>
+        <f t="shared" si="4"/>
         <v>-0.437583</v>
       </c>
       <c r="T25" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U25" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-8.5090800000000009</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>23</v>
       </c>
@@ -5001,19 +7643,19 @@
         <v>-1.06284</v>
       </c>
       <c r="S26" s="5">
-        <f>H26/1000000</f>
+        <f t="shared" si="4"/>
         <v>-0.289439</v>
       </c>
       <c r="T26" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U26" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-8.1559500000000007</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>24</v>
       </c>
@@ -5060,19 +7702,19 @@
         <v>-1.0546800000000001</v>
       </c>
       <c r="S27" s="2">
-        <f>H27/1000000</f>
+        <f t="shared" si="4"/>
         <v>-0.164159</v>
       </c>
       <c r="T27" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U27" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-7.8340500000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>25</v>
       </c>
@@ -5119,19 +7761,19 @@
         <v>-0.98041699999999998</v>
       </c>
       <c r="S28" s="2">
-        <f>H28/1000000</f>
+        <f t="shared" si="4"/>
         <v>1.8563700000000002E-2</v>
       </c>
       <c r="T28" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U28" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-7.4629599999999998</v>
       </c>
     </row>
-    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="J33" t="s">
         <v>11</v>
       </c>
@@ -5142,7 +7784,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="J34">
         <v>1</v>
       </c>
@@ -5153,7 +7795,16 @@
         <v>-13557300</v>
       </c>
     </row>
-    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B35">
+        <v>4.3</v>
+      </c>
+      <c r="C35">
+        <v>2.1</v>
+      </c>
+      <c r="D35">
+        <v>0.7</v>
+      </c>
       <c r="J35">
         <v>2</v>
       </c>
@@ -5164,7 +7815,7 @@
         <v>9961670</v>
       </c>
     </row>
-    <row r="36" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="J36">
         <v>3</v>
       </c>
@@ -5175,7 +7826,19 @@
         <v>2253980</v>
       </c>
     </row>
-    <row r="37" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C37" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" t="s">
+        <v>16</v>
+      </c>
       <c r="J37">
         <v>4</v>
       </c>
@@ -5186,7 +7849,23 @@
         <v>1306930</v>
       </c>
     </row>
-    <row r="38" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <f>E35</f>
+        <v>0</v>
+      </c>
       <c r="J38">
         <v>5</v>
       </c>
@@ -5197,7 +7876,27 @@
         <v>676313</v>
       </c>
     </row>
-    <row r="39" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B39">
+        <f>B38+1</f>
+        <v>2</v>
+      </c>
+      <c r="C39">
+        <f>B35</f>
+        <v>4.3</v>
+      </c>
+      <c r="D39">
+        <f>C39</f>
+        <v>4.3</v>
+      </c>
+      <c r="E39">
+        <f>C35</f>
+        <v>2.1</v>
+      </c>
+      <c r="F39">
+        <f>F38+$B$35</f>
+        <v>4.3</v>
+      </c>
       <c r="J39">
         <v>6</v>
       </c>
@@ -5208,7 +7907,27 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="40" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B40">
+        <f t="shared" ref="B40:B80" si="13">B39+1</f>
+        <v>3</v>
+      </c>
+      <c r="C40">
+        <f>C39+$B$35</f>
+        <v>8.6</v>
+      </c>
+      <c r="D40">
+        <f t="shared" ref="D40:D49" si="14">C40</f>
+        <v>8.6</v>
+      </c>
+      <c r="E40">
+        <f>E39+$C$35</f>
+        <v>4.2</v>
+      </c>
+      <c r="F40">
+        <f t="shared" ref="F40:F48" si="15">F39+$B$35</f>
+        <v>8.6</v>
+      </c>
       <c r="J40">
         <v>7</v>
       </c>
@@ -5219,7 +7938,27 @@
         <v>2407.9699999999998</v>
       </c>
     </row>
-    <row r="41" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B41">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="C41">
+        <f t="shared" ref="C41:C50" si="16">C40+$B$35</f>
+        <v>12.899999999999999</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="14"/>
+        <v>12.899999999999999</v>
+      </c>
+      <c r="E41">
+        <f t="shared" ref="E41:E63" si="17">E40+$C$35</f>
+        <v>6.3000000000000007</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="15"/>
+        <v>12.899999999999999</v>
+      </c>
       <c r="J41">
         <v>8</v>
       </c>
@@ -5230,7 +7969,27 @@
         <v>-522389</v>
       </c>
     </row>
-    <row r="42" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B42">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="16"/>
+        <v>17.2</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="14"/>
+        <v>17.2</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="17"/>
+        <v>8.4</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="15"/>
+        <v>17.2</v>
+      </c>
       <c r="J42">
         <v>9</v>
       </c>
@@ -5241,7 +8000,27 @@
         <v>-691240</v>
       </c>
     </row>
-    <row r="43" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B43">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="16"/>
+        <v>21.5</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="14"/>
+        <v>21.5</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="17"/>
+        <v>10.5</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="15"/>
+        <v>21.5</v>
+      </c>
       <c r="J43">
         <v>10</v>
       </c>
@@ -5252,7 +8031,27 @@
         <v>-865807</v>
       </c>
     </row>
-    <row r="44" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B44">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="16"/>
+        <v>25.8</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="14"/>
+        <v>25.8</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="17"/>
+        <v>12.6</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="15"/>
+        <v>25.8</v>
+      </c>
       <c r="J44" s="1">
         <v>11</v>
       </c>
@@ -5263,7 +8062,27 @@
         <v>-1046480</v>
       </c>
     </row>
-    <row r="45" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B45">
+        <f t="shared" si="13"/>
+        <v>8</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="16"/>
+        <v>30.1</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="14"/>
+        <v>30.1</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="17"/>
+        <v>14.7</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="15"/>
+        <v>30.1</v>
+      </c>
       <c r="J45" s="1">
         <v>12</v>
       </c>
@@ -5274,7 +8093,27 @@
         <v>-23018800</v>
       </c>
     </row>
-    <row r="46" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B46">
+        <f t="shared" si="13"/>
+        <v>9</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="16"/>
+        <v>34.4</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="14"/>
+        <v>34.4</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="17"/>
+        <v>16.8</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="15"/>
+        <v>34.4</v>
+      </c>
       <c r="J46" s="1">
         <v>13</v>
       </c>
@@ -5285,7 +8124,27 @@
         <v>-10077300</v>
       </c>
     </row>
-    <row r="47" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B47">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="16"/>
+        <v>38.699999999999996</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="14"/>
+        <v>38.699999999999996</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="17"/>
+        <v>18.900000000000002</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="15"/>
+        <v>38.699999999999996</v>
+      </c>
       <c r="J47" s="1">
         <v>14</v>
       </c>
@@ -5296,7 +8155,27 @@
         <v>2742620</v>
       </c>
     </row>
-    <row r="48" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B48">
+        <f t="shared" si="13"/>
+        <v>11</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="16"/>
+        <v>42.999999999999993</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="14"/>
+        <v>42.999999999999993</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="17"/>
+        <v>21.000000000000004</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="15"/>
+        <v>42.999999999999993</v>
+      </c>
       <c r="J48">
         <v>15</v>
       </c>
@@ -5307,7 +8186,26 @@
         <v>2734160</v>
       </c>
     </row>
-    <row r="49" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B49">
+        <f t="shared" si="13"/>
+        <v>12</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="16"/>
+        <v>47.29999999999999</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="14"/>
+        <v>47.29999999999999</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="17"/>
+        <v>23.100000000000005</v>
+      </c>
+      <c r="F49">
+        <v>47.3</v>
+      </c>
       <c r="J49">
         <v>16</v>
       </c>
@@ -5318,7 +8216,26 @@
         <v>2725150</v>
       </c>
     </row>
-    <row r="50" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B50">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="C50">
+        <f>C49+$C$35</f>
+        <v>49.399999999999991</v>
+      </c>
+      <c r="D50">
+        <f>E50</f>
+        <v>25.200000000000006</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="17"/>
+        <v>25.200000000000006</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
       <c r="J50">
         <v>17</v>
       </c>
@@ -5329,7 +8246,27 @@
         <v>2704980</v>
       </c>
     </row>
-    <row r="51" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B51">
+        <f t="shared" si="13"/>
+        <v>14</v>
+      </c>
+      <c r="C51">
+        <f t="shared" ref="C51:C63" si="18">C50+$C$35</f>
+        <v>51.499999999999993</v>
+      </c>
+      <c r="D51">
+        <f>E51</f>
+        <v>27.300000000000008</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="17"/>
+        <v>27.300000000000008</v>
+      </c>
+      <c r="F51">
+        <f>D35</f>
+        <v>0.7</v>
+      </c>
       <c r="J51">
         <v>18</v>
       </c>
@@ -5340,7 +8277,27 @@
         <v>2684220</v>
       </c>
     </row>
-    <row r="52" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B52">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="18"/>
+        <v>53.599999999999994</v>
+      </c>
+      <c r="D52">
+        <f t="shared" ref="D52:D63" si="19">E52</f>
+        <v>29.400000000000009</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="17"/>
+        <v>29.400000000000009</v>
+      </c>
+      <c r="F52">
+        <f>F51+$D$35</f>
+        <v>1.4</v>
+      </c>
       <c r="J52">
         <v>19</v>
       </c>
@@ -5351,7 +8308,27 @@
         <v>2673250</v>
       </c>
     </row>
-    <row r="53" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B53">
+        <f t="shared" si="13"/>
+        <v>16</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="18"/>
+        <v>55.699999999999996</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="19"/>
+        <v>31.500000000000011</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="17"/>
+        <v>31.500000000000011</v>
+      </c>
+      <c r="F53">
+        <f>F52+$D$35</f>
+        <v>2.0999999999999996</v>
+      </c>
       <c r="J53">
         <v>20</v>
       </c>
@@ -5362,7 +8339,27 @@
         <v>2661600</v>
       </c>
     </row>
-    <row r="54" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B54">
+        <f t="shared" si="13"/>
+        <v>17</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="18"/>
+        <v>57.8</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="19"/>
+        <v>33.600000000000009</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="17"/>
+        <v>33.600000000000009</v>
+      </c>
+      <c r="F54">
+        <f>F53+$D$35</f>
+        <v>2.8</v>
+      </c>
       <c r="J54" s="1">
         <v>21</v>
       </c>
@@ -5373,7 +8370,27 @@
         <v>2649260</v>
       </c>
     </row>
-    <row r="55" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B55">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="18"/>
+        <v>59.9</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="19"/>
+        <v>35.70000000000001</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="17"/>
+        <v>35.70000000000001</v>
+      </c>
+      <c r="F55">
+        <f>F54+$D$35</f>
+        <v>3.5</v>
+      </c>
       <c r="J55" s="1">
         <v>22</v>
       </c>
@@ -5384,7 +8401,27 @@
         <v>2630080</v>
       </c>
     </row>
-    <row r="56" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B56">
+        <f t="shared" si="13"/>
+        <v>19</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="18"/>
+        <v>62</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="19"/>
+        <v>37.800000000000011</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="17"/>
+        <v>37.800000000000011</v>
+      </c>
+      <c r="F56">
+        <f>F55+$D$35</f>
+        <v>4.2</v>
+      </c>
       <c r="J56">
         <v>23</v>
       </c>
@@ -5395,7 +8432,27 @@
         <v>2610170</v>
       </c>
     </row>
-    <row r="57" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B57">
+        <f t="shared" si="13"/>
+        <v>20</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="18"/>
+        <v>64.099999999999994</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="19"/>
+        <v>39.900000000000013</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="17"/>
+        <v>39.900000000000013</v>
+      </c>
+      <c r="F57">
+        <f>F56+$D$35</f>
+        <v>4.9000000000000004</v>
+      </c>
       <c r="J57" s="1">
         <v>24</v>
       </c>
@@ -5406,7 +8463,27 @@
         <v>2595680</v>
       </c>
     </row>
-    <row r="58" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B58">
+        <f t="shared" si="13"/>
+        <v>21</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="18"/>
+        <v>66.199999999999989</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="19"/>
+        <v>42.000000000000014</v>
+      </c>
+      <c r="E58">
+        <f t="shared" si="17"/>
+        <v>42.000000000000014</v>
+      </c>
+      <c r="F58">
+        <f>F57+$D$35</f>
+        <v>5.6000000000000005</v>
+      </c>
       <c r="J58" s="1">
         <v>25</v>
       </c>
@@ -5417,7 +8494,27 @@
         <v>2580430</v>
       </c>
     </row>
-    <row r="59" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B59">
+        <f t="shared" si="13"/>
+        <v>22</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="18"/>
+        <v>68.299999999999983</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="19"/>
+        <v>44.100000000000016</v>
+      </c>
+      <c r="E59">
+        <f t="shared" si="17"/>
+        <v>44.100000000000016</v>
+      </c>
+      <c r="F59">
+        <f>F58+$D$35</f>
+        <v>6.3000000000000007</v>
+      </c>
       <c r="J59" s="1">
         <v>26</v>
       </c>
@@ -5428,41 +8525,231 @@
         <v>3244240</v>
       </c>
     </row>
-    <row r="60" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B60">
+        <f t="shared" si="13"/>
+        <v>23</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="18"/>
+        <v>70.399999999999977</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="19"/>
+        <v>46.200000000000017</v>
+      </c>
+      <c r="E60">
+        <f t="shared" si="17"/>
+        <v>46.200000000000017</v>
+      </c>
+      <c r="F60">
+        <f>F59+$D$35</f>
+        <v>7.0000000000000009</v>
+      </c>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
     </row>
-    <row r="61" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B61">
+        <f t="shared" si="13"/>
+        <v>24</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="18"/>
+        <v>72.499999999999972</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="19"/>
+        <v>48.300000000000018</v>
+      </c>
+      <c r="E61">
+        <f t="shared" si="17"/>
+        <v>48.300000000000018</v>
+      </c>
+      <c r="F61">
+        <f>F60+$D$35</f>
+        <v>7.7000000000000011</v>
+      </c>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
     </row>
-    <row r="62" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B62">
+        <f t="shared" si="13"/>
+        <v>25</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="18"/>
+        <v>74.599999999999966</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="19"/>
+        <v>50.40000000000002</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="17"/>
+        <v>50.40000000000002</v>
+      </c>
+      <c r="F62">
+        <f>F61+$D$35</f>
+        <v>8.4</v>
+      </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
     </row>
-    <row r="63" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B63">
+        <f t="shared" si="13"/>
+        <v>26</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="18"/>
+        <v>76.69999999999996</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="19"/>
+        <v>52.500000000000021</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="17"/>
+        <v>52.500000000000021</v>
+      </c>
+      <c r="F63">
+        <f>F62+$D$35</f>
+        <v>9.1</v>
+      </c>
       <c r="J63" s="1"/>
     </row>
-    <row r="64" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B64">
+        <f t="shared" si="13"/>
+        <v>27</v>
+      </c>
+      <c r="F64">
+        <f>F63+$D$35</f>
+        <v>9.7999999999999989</v>
+      </c>
       <c r="J64" s="1"/>
     </row>
-    <row r="65" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B65">
+        <f t="shared" si="13"/>
+        <v>28</v>
+      </c>
+      <c r="F65">
+        <f>F64+$D$35</f>
+        <v>10.499999999999998</v>
+      </c>
       <c r="J65" s="1"/>
     </row>
-    <row r="66" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B66">
+        <f t="shared" si="13"/>
+        <v>29</v>
+      </c>
+      <c r="F66">
+        <f>F65+$D$35</f>
+        <v>11.199999999999998</v>
+      </c>
       <c r="J66" s="1"/>
     </row>
-    <row r="67" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B67">
+        <f t="shared" si="13"/>
+        <v>30</v>
+      </c>
+      <c r="F67">
+        <f>F66+$D$35</f>
+        <v>11.899999999999997</v>
+      </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
     </row>
-    <row r="68" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B68">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="F68">
+        <f>F67+$D$35</f>
+        <v>12.599999999999996</v>
+      </c>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
     </row>
-    <row r="69" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B69">
+        <f t="shared" si="13"/>
+        <v>32</v>
+      </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B70">
+        <f t="shared" si="13"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B71">
+        <f t="shared" si="13"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B72">
+        <f t="shared" si="13"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B73">
+        <f t="shared" si="13"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B74">
+        <f t="shared" si="13"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B75">
+        <f t="shared" si="13"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B76">
+        <f t="shared" si="13"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B77">
+        <f t="shared" si="13"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B78">
+        <f t="shared" si="13"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B79">
+        <f t="shared" si="13"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B80">
+        <f t="shared" si="13"/>
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5470,27 +8757,2874 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8baa01ab-7cf8-4360-9f3f-f87b1ec95c26">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d481fc2a-e230-47f7-a716-4f7f4b27a8e6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E164573A-5CCB-4F9D-A147-E338BA79484A}">
+  <dimension ref="A1:Z69"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.7265625" customWidth="1"/>
+    <col min="7" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="17" max="17" width="3.26953125" customWidth="1"/>
+    <col min="22" max="22" width="2.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R1" t="s">
+        <v>5</v>
+      </c>
+      <c r="W1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N2" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S2" t="s">
+        <v>10</v>
+      </c>
+      <c r="T2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U2" t="s">
+        <v>8</v>
+      </c>
+      <c r="W2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1">
+        <v>-13557300</v>
+      </c>
+      <c r="C3" s="1">
+        <v>-13557300</v>
+      </c>
+      <c r="D3" s="1">
+        <v>-13557300</v>
+      </c>
+      <c r="E3" s="1">
+        <v>-13557300</v>
+      </c>
+      <c r="G3" s="1">
+        <v>-13557300</v>
+      </c>
+      <c r="H3" s="1">
+        <v>-13557300</v>
+      </c>
+      <c r="I3" s="1">
+        <v>-13557300</v>
+      </c>
+      <c r="J3" s="1">
+        <v>-13557300</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
+        <f>B3/1000000</f>
+        <v>-13.5573</v>
+      </c>
+      <c r="N3" s="2">
+        <f>C3/1000000</f>
+        <v>-13.5573</v>
+      </c>
+      <c r="O3" s="2">
+        <f>D3/1000000</f>
+        <v>-13.5573</v>
+      </c>
+      <c r="P3" s="2">
+        <f>E3/1000000</f>
+        <v>-13.5573</v>
+      </c>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2">
+        <f>G3/1000000</f>
+        <v>-13.5573</v>
+      </c>
+      <c r="S3" s="2">
+        <f>H3/1000000</f>
+        <v>-13.5573</v>
+      </c>
+      <c r="T3" s="2">
+        <f>I3/1000000</f>
+        <v>-13.5573</v>
+      </c>
+      <c r="U3" s="2">
+        <f>J3/1000000</f>
+        <v>-13.5573</v>
+      </c>
+      <c r="W3" s="3">
+        <f>M3</f>
+        <v>-13.5573</v>
+      </c>
+      <c r="X3" s="3">
+        <f>N3</f>
+        <v>-13.5573</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>O3</f>
+        <v>-13.5573</v>
+      </c>
+      <c r="Z3" s="3">
+        <f>P3</f>
+        <v>-13.5573</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>9961670</v>
+      </c>
+      <c r="C4" s="1">
+        <v>9961670</v>
+      </c>
+      <c r="D4" s="1">
+        <v>9961670</v>
+      </c>
+      <c r="E4" s="1">
+        <v>9961670</v>
+      </c>
+      <c r="G4" s="1">
+        <v>-4423200</v>
+      </c>
+      <c r="H4" s="1">
+        <v>-4423200</v>
+      </c>
+      <c r="I4" s="1">
+        <v>-4423200</v>
+      </c>
+      <c r="J4" s="1">
+        <v>-4423200</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2">
+        <f t="shared" ref="M4:P28" si="0">B4/1000000</f>
+        <v>9.9616699999999998</v>
+      </c>
+      <c r="N4" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9616699999999998</v>
+      </c>
+      <c r="O4" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9616699999999998</v>
+      </c>
+      <c r="P4" s="2">
+        <f t="shared" si="0"/>
+        <v>9.9616699999999998</v>
+      </c>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2">
+        <f t="shared" ref="R4:U28" si="1">G4/1000000</f>
+        <v>-4.4231999999999996</v>
+      </c>
+      <c r="S4" s="2">
+        <f t="shared" si="1"/>
+        <v>-4.4231999999999996</v>
+      </c>
+      <c r="T4" s="2">
+        <f t="shared" si="1"/>
+        <v>-4.4231999999999996</v>
+      </c>
+      <c r="U4" s="2">
+        <f t="shared" si="1"/>
+        <v>-4.4231999999999996</v>
+      </c>
+      <c r="W4" s="3">
+        <f>W3+M4</f>
+        <v>-3.5956299999999999</v>
+      </c>
+      <c r="X4" s="3">
+        <f>X3+N4</f>
+        <v>-3.5956299999999999</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>Y3+O4</f>
+        <v>-3.5956299999999999</v>
+      </c>
+      <c r="Z4" s="3">
+        <f>Z3+P4</f>
+        <v>-3.5956299999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2363110</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2363110</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2363110</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2363110</v>
+      </c>
+      <c r="G5" s="1">
+        <v>-2436410</v>
+      </c>
+      <c r="H5" s="1">
+        <v>-2436410</v>
+      </c>
+      <c r="I5" s="1">
+        <v>-2436410</v>
+      </c>
+      <c r="J5" s="1">
+        <v>-2436410</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="2">
+        <f t="shared" si="0"/>
+        <v>2.3631099999999998</v>
+      </c>
+      <c r="N5" s="2">
+        <f t="shared" si="0"/>
+        <v>2.3631099999999998</v>
+      </c>
+      <c r="O5" s="2">
+        <f t="shared" si="0"/>
+        <v>2.3631099999999998</v>
+      </c>
+      <c r="P5" s="2">
+        <f t="shared" si="0"/>
+        <v>2.3631099999999998</v>
+      </c>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2">
+        <f t="shared" si="1"/>
+        <v>-2.43641</v>
+      </c>
+      <c r="S5" s="2">
+        <f t="shared" si="1"/>
+        <v>-2.43641</v>
+      </c>
+      <c r="T5" s="2">
+        <f t="shared" si="1"/>
+        <v>-2.43641</v>
+      </c>
+      <c r="U5" s="2">
+        <f t="shared" si="1"/>
+        <v>-2.43641</v>
+      </c>
+      <c r="W5" s="3">
+        <f t="shared" ref="W5:Z20" si="2">W4+M5</f>
+        <v>-1.2325200000000001</v>
+      </c>
+      <c r="X5" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.2325200000000001</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.2325200000000001</v>
+      </c>
+      <c r="Z5" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.2325200000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1527440</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1527440</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1527440</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1527440</v>
+      </c>
+      <c r="G6" s="1">
+        <v>-1258890</v>
+      </c>
+      <c r="H6" s="1">
+        <v>-1258890</v>
+      </c>
+      <c r="I6" s="1">
+        <v>-1258890</v>
+      </c>
+      <c r="J6" s="1">
+        <v>-1258890</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6" s="2">
+        <f t="shared" si="0"/>
+        <v>1.5274399999999999</v>
+      </c>
+      <c r="N6" s="2">
+        <f t="shared" si="0"/>
+        <v>1.5274399999999999</v>
+      </c>
+      <c r="O6" s="2">
+        <f t="shared" si="0"/>
+        <v>1.5274399999999999</v>
+      </c>
+      <c r="P6" s="2">
+        <f t="shared" si="0"/>
+        <v>1.5274399999999999</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.2588900000000001</v>
+      </c>
+      <c r="S6" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.2588900000000001</v>
+      </c>
+      <c r="T6" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.2588900000000001</v>
+      </c>
+      <c r="U6" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.2588900000000001</v>
+      </c>
+      <c r="W6" s="3">
+        <f t="shared" si="2"/>
+        <v>0.29491999999999985</v>
+      </c>
+      <c r="X6" s="3">
+        <f t="shared" si="2"/>
+        <v>0.29491999999999985</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0.29491999999999985</v>
+      </c>
+      <c r="Z6" s="3">
+        <f t="shared" si="2"/>
+        <v>0.29491999999999985</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>994514</v>
+      </c>
+      <c r="C7">
+        <v>994514</v>
+      </c>
+      <c r="D7" s="1">
+        <v>994514</v>
+      </c>
+      <c r="E7" s="1">
+        <v>994514</v>
+      </c>
+      <c r="G7" s="1">
+        <v>-555898</v>
+      </c>
+      <c r="H7" s="1">
+        <v>-555898</v>
+      </c>
+      <c r="I7" s="1">
+        <v>-555898</v>
+      </c>
+      <c r="J7" s="1">
+        <v>-555898</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7" s="2">
+        <f t="shared" si="0"/>
+        <v>0.99451400000000001</v>
+      </c>
+      <c r="N7" s="2">
+        <f t="shared" si="0"/>
+        <v>0.99451400000000001</v>
+      </c>
+      <c r="O7" s="2">
+        <f t="shared" si="0"/>
+        <v>0.99451400000000001</v>
+      </c>
+      <c r="P7" s="2">
+        <f t="shared" si="0"/>
+        <v>0.99451400000000001</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.555898</v>
+      </c>
+      <c r="S7" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.555898</v>
+      </c>
+      <c r="T7" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.555898</v>
+      </c>
+      <c r="U7" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.555898</v>
+      </c>
+      <c r="W7" s="3">
+        <f t="shared" si="2"/>
+        <v>1.289434</v>
+      </c>
+      <c r="X7" s="3">
+        <f t="shared" si="2"/>
+        <v>1.289434</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>1.289434</v>
+      </c>
+      <c r="Z7" s="3">
+        <f t="shared" si="2"/>
+        <v>1.289434</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>940185</v>
+      </c>
+      <c r="C8">
+        <v>940185</v>
+      </c>
+      <c r="D8" s="1">
+        <v>940185</v>
+      </c>
+      <c r="E8" s="1">
+        <v>940185</v>
+      </c>
+      <c r="G8" s="1">
+        <v>53478.7</v>
+      </c>
+      <c r="H8">
+        <v>53478.7</v>
+      </c>
+      <c r="I8" s="1">
+        <v>53478.7</v>
+      </c>
+      <c r="J8" s="1">
+        <v>53478.7</v>
+      </c>
+      <c r="L8">
+        <v>5</v>
+      </c>
+      <c r="M8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.94018500000000005</v>
+      </c>
+      <c r="N8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.94018500000000005</v>
+      </c>
+      <c r="O8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.94018500000000005</v>
+      </c>
+      <c r="P8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.94018500000000005</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2">
+        <f t="shared" si="1"/>
+        <v>5.3478699999999997E-2</v>
+      </c>
+      <c r="S8" s="2">
+        <f t="shared" si="1"/>
+        <v>5.3478699999999997E-2</v>
+      </c>
+      <c r="T8" s="2">
+        <f t="shared" si="1"/>
+        <v>5.3478699999999997E-2</v>
+      </c>
+      <c r="U8" s="2">
+        <f t="shared" si="1"/>
+        <v>5.3478699999999997E-2</v>
+      </c>
+      <c r="W8" s="3">
+        <f t="shared" si="2"/>
+        <v>2.229619</v>
+      </c>
+      <c r="X8" s="3">
+        <f t="shared" si="2"/>
+        <v>2.229619</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>2.229619</v>
+      </c>
+      <c r="Z8" s="3">
+        <f t="shared" si="2"/>
+        <v>2.229619</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>518517</v>
+      </c>
+      <c r="C9">
+        <v>518517</v>
+      </c>
+      <c r="D9" s="1">
+        <v>518517</v>
+      </c>
+      <c r="E9" s="1">
+        <v>518517</v>
+      </c>
+      <c r="G9" s="1">
+        <v>361634</v>
+      </c>
+      <c r="H9">
+        <v>361634</v>
+      </c>
+      <c r="I9" s="1">
+        <v>361634</v>
+      </c>
+      <c r="J9" s="1">
+        <v>361634</v>
+      </c>
+      <c r="L9">
+        <v>6</v>
+      </c>
+      <c r="M9" s="2">
+        <f t="shared" si="0"/>
+        <v>0.51851700000000001</v>
+      </c>
+      <c r="N9" s="2">
+        <f t="shared" si="0"/>
+        <v>0.51851700000000001</v>
+      </c>
+      <c r="O9" s="2">
+        <f t="shared" si="0"/>
+        <v>0.51851700000000001</v>
+      </c>
+      <c r="P9" s="2">
+        <f t="shared" si="0"/>
+        <v>0.51851700000000001</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2">
+        <f t="shared" si="1"/>
+        <v>0.36163400000000001</v>
+      </c>
+      <c r="S9" s="2">
+        <f t="shared" si="1"/>
+        <v>0.36163400000000001</v>
+      </c>
+      <c r="T9" s="2">
+        <f t="shared" si="1"/>
+        <v>0.36163400000000001</v>
+      </c>
+      <c r="U9" s="2">
+        <f t="shared" si="1"/>
+        <v>0.36163400000000001</v>
+      </c>
+      <c r="W9" s="3">
+        <f t="shared" si="2"/>
+        <v>2.7481360000000001</v>
+      </c>
+      <c r="X9" s="3">
+        <f t="shared" si="2"/>
+        <v>2.7481360000000001</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>2.7481360000000001</v>
+      </c>
+      <c r="Z9" s="3">
+        <f t="shared" si="2"/>
+        <v>2.7481360000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>25097.8</v>
+      </c>
+      <c r="C10" s="1">
+        <v>25097.8</v>
+      </c>
+      <c r="D10">
+        <v>25097.8</v>
+      </c>
+      <c r="E10" s="1">
+        <v>25097.8</v>
+      </c>
+      <c r="G10" s="1">
+        <v>375311</v>
+      </c>
+      <c r="H10">
+        <v>375311</v>
+      </c>
+      <c r="I10" s="1">
+        <v>375311</v>
+      </c>
+      <c r="J10">
+        <v>375311</v>
+      </c>
+      <c r="L10">
+        <v>7</v>
+      </c>
+      <c r="M10" s="2">
+        <f t="shared" si="0"/>
+        <v>2.50978E-2</v>
+      </c>
+      <c r="N10" s="2">
+        <f t="shared" si="0"/>
+        <v>2.50978E-2</v>
+      </c>
+      <c r="O10" s="2">
+        <f t="shared" si="0"/>
+        <v>2.50978E-2</v>
+      </c>
+      <c r="P10" s="2">
+        <f t="shared" si="0"/>
+        <v>2.50978E-2</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2">
+        <f t="shared" si="1"/>
+        <v>0.37531100000000001</v>
+      </c>
+      <c r="S10" s="2">
+        <f t="shared" si="1"/>
+        <v>0.37531100000000001</v>
+      </c>
+      <c r="T10" s="2">
+        <f t="shared" si="1"/>
+        <v>0.37531100000000001</v>
+      </c>
+      <c r="U10" s="2">
+        <f t="shared" si="1"/>
+        <v>0.37531100000000001</v>
+      </c>
+      <c r="W10" s="3">
+        <f t="shared" si="2"/>
+        <v>2.7732338000000003</v>
+      </c>
+      <c r="X10" s="3">
+        <f t="shared" si="2"/>
+        <v>2.7732338000000003</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>2.7732338000000003</v>
+      </c>
+      <c r="Z10" s="3">
+        <f t="shared" si="2"/>
+        <v>2.7732338000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>-621712</v>
+      </c>
+      <c r="C11" s="1">
+        <v>-621712</v>
+      </c>
+      <c r="D11">
+        <v>-621712</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-621712</v>
+      </c>
+      <c r="G11" s="1">
+        <v>64664.9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>64664.9</v>
+      </c>
+      <c r="I11" s="1">
+        <v>64664.9</v>
+      </c>
+      <c r="J11" s="1">
+        <v>64664.9</v>
+      </c>
+      <c r="L11">
+        <v>8</v>
+      </c>
+      <c r="M11" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.62171200000000004</v>
+      </c>
+      <c r="N11" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.62171200000000004</v>
+      </c>
+      <c r="O11" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.62171200000000004</v>
+      </c>
+      <c r="P11" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.62171200000000004</v>
+      </c>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2">
+        <f t="shared" si="1"/>
+        <v>6.4664899999999997E-2</v>
+      </c>
+      <c r="S11" s="2">
+        <f t="shared" si="1"/>
+        <v>6.4664899999999997E-2</v>
+      </c>
+      <c r="T11" s="2">
+        <f t="shared" si="1"/>
+        <v>6.4664899999999997E-2</v>
+      </c>
+      <c r="U11" s="2">
+        <f t="shared" si="1"/>
+        <v>6.4664899999999997E-2</v>
+      </c>
+      <c r="W11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.1515218000000003</v>
+      </c>
+      <c r="X11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.1515218000000003</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.1515218000000003</v>
+      </c>
+      <c r="Z11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.1515218000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-946058</v>
+      </c>
+      <c r="C12" s="1">
+        <v>-946058</v>
+      </c>
+      <c r="D12">
+        <v>-946058</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-946058</v>
+      </c>
+      <c r="G12" s="1">
+        <v>-368774</v>
+      </c>
+      <c r="H12" s="1">
+        <v>-368774</v>
+      </c>
+      <c r="I12" s="1">
+        <v>-368774</v>
+      </c>
+      <c r="J12" s="1">
+        <v>-368774</v>
+      </c>
+      <c r="L12">
+        <v>9</v>
+      </c>
+      <c r="M12" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.94605799999999995</v>
+      </c>
+      <c r="N12" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.94605799999999995</v>
+      </c>
+      <c r="O12" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.94605799999999995</v>
+      </c>
+      <c r="P12" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.94605799999999995</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.36877399999999999</v>
+      </c>
+      <c r="S12" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.36877399999999999</v>
+      </c>
+      <c r="T12" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.36877399999999999</v>
+      </c>
+      <c r="U12" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.36877399999999999</v>
+      </c>
+      <c r="W12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2054638000000004</v>
+      </c>
+      <c r="X12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2054638000000004</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2054638000000004</v>
+      </c>
+      <c r="Z12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2054638000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>-1127520</v>
+      </c>
+      <c r="C13" s="1">
+        <v>-1127520</v>
+      </c>
+      <c r="D13" s="1">
+        <v>-1127520</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-1127520</v>
+      </c>
+      <c r="G13" s="1">
+        <v>-842439</v>
+      </c>
+      <c r="H13" s="1">
+        <v>-842439</v>
+      </c>
+      <c r="I13" s="1">
+        <v>-842439</v>
+      </c>
+      <c r="J13" s="1">
+        <v>-842439</v>
+      </c>
+      <c r="L13">
+        <v>10</v>
+      </c>
+      <c r="M13" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.1275200000000001</v>
+      </c>
+      <c r="N13" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.1275200000000001</v>
+      </c>
+      <c r="O13" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.1275200000000001</v>
+      </c>
+      <c r="P13" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.1275200000000001</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.84243900000000005</v>
+      </c>
+      <c r="S13" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.84243900000000005</v>
+      </c>
+      <c r="T13" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.84243900000000005</v>
+      </c>
+      <c r="U13" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.84243900000000005</v>
+      </c>
+      <c r="W13" s="3">
+        <f t="shared" si="2"/>
+        <v>7.7943800000000341E-2</v>
+      </c>
+      <c r="X13" s="3">
+        <f t="shared" si="2"/>
+        <v>7.7943800000000341E-2</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>7.7943800000000341E-2</v>
+      </c>
+      <c r="Z13" s="3">
+        <f t="shared" si="2"/>
+        <v>7.7943800000000341E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>-1315260</v>
+      </c>
+      <c r="C14" s="1">
+        <v>-3749660</v>
+      </c>
+      <c r="D14" s="1">
+        <v>-4411110</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-23100600</v>
+      </c>
+      <c r="G14" s="1">
+        <v>-1349070</v>
+      </c>
+      <c r="H14" s="1">
+        <v>-2286780</v>
+      </c>
+      <c r="I14" s="1">
+        <v>-2541570</v>
+      </c>
+      <c r="J14" s="1">
+        <v>-9740650</v>
+      </c>
+      <c r="L14">
+        <v>11</v>
+      </c>
+      <c r="M14" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.3152600000000001</v>
+      </c>
+      <c r="N14" s="2">
+        <f t="shared" si="0"/>
+        <v>-3.74966</v>
+      </c>
+      <c r="O14" s="2">
+        <f t="shared" si="0"/>
+        <v>-4.4111099999999999</v>
+      </c>
+      <c r="P14" s="2">
+        <f t="shared" si="0"/>
+        <v>-23.1006</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.34907</v>
+      </c>
+      <c r="S14" s="2">
+        <f t="shared" si="1"/>
+        <v>-2.2867799999999998</v>
+      </c>
+      <c r="T14" s="2">
+        <f t="shared" si="1"/>
+        <v>-2.5415700000000001</v>
+      </c>
+      <c r="U14" s="2">
+        <f t="shared" si="1"/>
+        <v>-9.7406500000000005</v>
+      </c>
+      <c r="W14" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.2373161999999998</v>
+      </c>
+      <c r="X14" s="3">
+        <f t="shared" si="2"/>
+        <v>-3.6717161999999997</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>-4.3331661999999991</v>
+      </c>
+      <c r="Z14" s="3">
+        <f t="shared" si="2"/>
+        <v>-23.0226562</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>-213974</v>
+      </c>
+      <c r="C15" s="1">
+        <v>-1325380</v>
+      </c>
+      <c r="D15" s="1">
+        <v>-1134190</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-10159900</v>
+      </c>
+      <c r="G15" s="1">
+        <v>-1424640</v>
+      </c>
+      <c r="H15" s="1">
+        <v>-2754900</v>
+      </c>
+      <c r="I15" s="1">
+        <v>-2942160</v>
+      </c>
+      <c r="J15" s="1">
+        <v>-13329100</v>
+      </c>
+      <c r="L15">
+        <v>12</v>
+      </c>
+      <c r="M15" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.213974</v>
+      </c>
+      <c r="N15" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.32538</v>
+      </c>
+      <c r="O15" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.13419</v>
+      </c>
+      <c r="P15" s="2">
+        <f t="shared" si="0"/>
+        <v>-10.1599</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.4246399999999999</v>
+      </c>
+      <c r="S15" s="2">
+        <f t="shared" si="1"/>
+        <v>-2.7549000000000001</v>
+      </c>
+      <c r="T15" s="5">
+        <f t="shared" si="1"/>
+        <v>-2.9421599999999999</v>
+      </c>
+      <c r="U15" s="2">
+        <f t="shared" si="1"/>
+        <v>-13.3291</v>
+      </c>
+      <c r="W15" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.4512901999999999</v>
+      </c>
+      <c r="X15" s="3">
+        <f t="shared" si="2"/>
+        <v>-4.9970961999999997</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>-5.4673561999999993</v>
+      </c>
+      <c r="Z15" s="4">
+        <f>Z14+P15</f>
+        <v>-33.182556200000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>940264</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1636070</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2742620</v>
+      </c>
+      <c r="G16" s="1">
+        <v>-1120130</v>
+      </c>
+      <c r="H16" s="1">
+        <v>-2225050</v>
+      </c>
+      <c r="J16" s="1">
+        <v>-12440900</v>
+      </c>
+      <c r="L16">
+        <v>13</v>
+      </c>
+      <c r="M16" s="2">
+        <f t="shared" si="0"/>
+        <v>0.94026399999999999</v>
+      </c>
+      <c r="N16" s="2">
+        <f t="shared" si="0"/>
+        <v>1.6360699999999999</v>
+      </c>
+      <c r="O16" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="2">
+        <f t="shared" si="0"/>
+        <v>2.7426200000000001</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.1201300000000001</v>
+      </c>
+      <c r="S16" s="2">
+        <f t="shared" si="1"/>
+        <v>-2.22505</v>
+      </c>
+      <c r="T16" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="2">
+        <f t="shared" si="1"/>
+        <v>-12.440899999999999</v>
+      </c>
+      <c r="W16" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.51102619999999987</v>
+      </c>
+      <c r="X16" s="3">
+        <f t="shared" si="2"/>
+        <v>-3.3610261999999995</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>-5.4673561999999993</v>
+      </c>
+      <c r="Z16" s="3">
+        <f t="shared" si="2"/>
+        <v>-30.439936200000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>864571</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1567310</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2734160</v>
+      </c>
+      <c r="G17" s="1">
+        <v>-863400</v>
+      </c>
+      <c r="H17" s="1">
+        <v>-1759640</v>
+      </c>
+      <c r="J17" s="1">
+        <v>-11629000</v>
+      </c>
+      <c r="L17">
+        <v>14</v>
+      </c>
+      <c r="M17" s="2">
+        <f t="shared" si="0"/>
+        <v>0.86457099999999998</v>
+      </c>
+      <c r="N17" s="2">
+        <f t="shared" si="0"/>
+        <v>1.56731</v>
+      </c>
+      <c r="O17" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="2">
+        <f t="shared" si="0"/>
+        <v>2.7341600000000001</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.86339999999999995</v>
+      </c>
+      <c r="S17" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.7596400000000001</v>
+      </c>
+      <c r="T17" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="2">
+        <f t="shared" si="1"/>
+        <v>-11.629</v>
+      </c>
+      <c r="W17" s="3">
+        <f t="shared" si="2"/>
+        <v>0.3535448000000001</v>
+      </c>
+      <c r="X17" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.7937161999999995</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>-5.4673561999999993</v>
+      </c>
+      <c r="Z17" s="3">
+        <f t="shared" si="2"/>
+        <v>-27.705776200000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>787178</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1496910</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2725150</v>
+      </c>
+      <c r="G18" s="1">
+        <v>-649066</v>
+      </c>
+      <c r="H18" s="1">
+        <v>-1352060</v>
+      </c>
+      <c r="J18" s="1">
+        <v>-10887000</v>
+      </c>
+      <c r="L18">
+        <v>15</v>
+      </c>
+      <c r="M18" s="2">
+        <f t="shared" si="0"/>
+        <v>0.78717800000000004</v>
+      </c>
+      <c r="N18" s="2">
+        <f t="shared" si="0"/>
+        <v>1.49691</v>
+      </c>
+      <c r="O18" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="2">
+        <f t="shared" si="0"/>
+        <v>2.7251500000000002</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.64906600000000003</v>
+      </c>
+      <c r="S18" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.35206</v>
+      </c>
+      <c r="T18" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="2">
+        <f t="shared" si="1"/>
+        <v>-10.887</v>
+      </c>
+      <c r="W18" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1407228000000003</v>
+      </c>
+      <c r="X18" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.29680619999999958</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>-5.4673561999999993</v>
+      </c>
+      <c r="Z18" s="3">
+        <f t="shared" si="2"/>
+        <v>-24.980626200000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>697474</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1414270</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2704980</v>
+      </c>
+      <c r="G19" s="1">
+        <v>-474933</v>
+      </c>
+      <c r="H19" s="1">
+        <v>-998973</v>
+      </c>
+      <c r="J19" s="1">
+        <v>-10211600</v>
+      </c>
+      <c r="L19">
+        <v>16</v>
+      </c>
+      <c r="M19" s="2">
+        <f t="shared" si="0"/>
+        <v>0.69747400000000004</v>
+      </c>
+      <c r="N19" s="2">
+        <f t="shared" si="0"/>
+        <v>1.4142699999999999</v>
+      </c>
+      <c r="O19" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P19" s="2">
+        <f t="shared" si="0"/>
+        <v>2.7049799999999999</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.47493299999999999</v>
+      </c>
+      <c r="S19" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.998973</v>
+      </c>
+      <c r="T19" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="2">
+        <f t="shared" si="1"/>
+        <v>-10.211600000000001</v>
+      </c>
+      <c r="W19" s="3">
+        <f t="shared" si="2"/>
+        <v>1.8381968000000004</v>
+      </c>
+      <c r="X19" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1174638000000003</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>-5.4673561999999993</v>
+      </c>
+      <c r="Z19" s="3">
+        <f t="shared" si="2"/>
+        <v>-22.275646200000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>605972</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1329900</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2684220</v>
+      </c>
+      <c r="G20" s="1">
+        <v>-336213</v>
+      </c>
+      <c r="H20" s="1">
+        <v>-694531</v>
+      </c>
+      <c r="J20" s="1">
+        <v>-9597150</v>
+      </c>
+      <c r="L20">
+        <v>17</v>
+      </c>
+      <c r="M20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.60597199999999996</v>
+      </c>
+      <c r="N20" s="2">
+        <f t="shared" si="0"/>
+        <v>1.3299000000000001</v>
+      </c>
+      <c r="O20" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="2">
+        <f t="shared" si="0"/>
+        <v>2.6842199999999998</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.33621299999999998</v>
+      </c>
+      <c r="S20" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.69453100000000001</v>
+      </c>
+      <c r="T20" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="2">
+        <f t="shared" si="1"/>
+        <v>-9.5971499999999992</v>
+      </c>
+      <c r="W20" s="3">
+        <f t="shared" si="2"/>
+        <v>2.4441688000000004</v>
+      </c>
+      <c r="X20" s="3">
+        <f t="shared" si="2"/>
+        <v>2.4473638000000006</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>-5.4673561999999993</v>
+      </c>
+      <c r="Z20" s="3">
+        <f t="shared" si="2"/>
+        <v>-19.591426200000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>523056</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1254190</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2673250</v>
+      </c>
+      <c r="G21" s="1">
+        <v>-226422</v>
+      </c>
+      <c r="H21" s="1">
+        <v>-431271</v>
+      </c>
+      <c r="J21" s="1">
+        <v>-9036030</v>
+      </c>
+      <c r="L21">
+        <v>18</v>
+      </c>
+      <c r="M21" s="2">
+        <f t="shared" si="0"/>
+        <v>0.52305599999999997</v>
+      </c>
+      <c r="N21" s="2">
+        <f t="shared" si="0"/>
+        <v>1.2541899999999999</v>
+      </c>
+      <c r="O21" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P21" s="2">
+        <f t="shared" si="0"/>
+        <v>2.6732499999999999</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.22642200000000001</v>
+      </c>
+      <c r="S21" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.43127100000000002</v>
+      </c>
+      <c r="T21" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="2">
+        <f t="shared" si="1"/>
+        <v>-9.0360300000000002</v>
+      </c>
+      <c r="W21" s="3">
+        <f t="shared" ref="W21:Z23" si="3">W20+M21</f>
+        <v>2.9672248000000003</v>
+      </c>
+      <c r="X21" s="3">
+        <f t="shared" si="3"/>
+        <v>3.7015538000000006</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="3"/>
+        <v>-5.4673561999999993</v>
+      </c>
+      <c r="Z21" s="3">
+        <f t="shared" si="3"/>
+        <v>-16.918176200000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <v>438248</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1176650</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2661600</v>
+      </c>
+      <c r="G22" s="1">
+        <v>-142074</v>
+      </c>
+      <c r="H22" s="1">
+        <v>-204805</v>
+      </c>
+      <c r="J22" s="1">
+        <v>-8523760</v>
+      </c>
+      <c r="L22">
+        <v>19</v>
+      </c>
+      <c r="M22" s="2">
+        <f t="shared" si="0"/>
+        <v>0.43824800000000003</v>
+      </c>
+      <c r="N22" s="2">
+        <f t="shared" si="0"/>
+        <v>1.17665</v>
+      </c>
+      <c r="O22" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P22" s="2">
+        <f t="shared" si="0"/>
+        <v>2.6616</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.14207400000000001</v>
+      </c>
+      <c r="S22" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.20480499999999999</v>
+      </c>
+      <c r="T22" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="2">
+        <f t="shared" si="1"/>
+        <v>-8.5237599999999993</v>
+      </c>
+      <c r="W22" s="3">
+        <f t="shared" si="3"/>
+        <v>3.4054728000000005</v>
+      </c>
+      <c r="X22" s="3">
+        <f t="shared" si="3"/>
+        <v>4.8782038000000005</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="3"/>
+        <v>-5.4673561999999993</v>
+      </c>
+      <c r="Z22" s="3">
+        <f t="shared" si="3"/>
+        <v>-14.256576200000005</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1">
+        <v>351512</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1097260</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2649260</v>
+      </c>
+      <c r="G23" s="1">
+        <v>-80039.7</v>
+      </c>
+      <c r="H23">
+        <v>-11162</v>
+      </c>
+      <c r="J23" s="1">
+        <v>-8056220</v>
+      </c>
+      <c r="L23">
+        <v>20</v>
+      </c>
+      <c r="M23" s="2">
+        <f t="shared" si="0"/>
+        <v>0.35151199999999999</v>
+      </c>
+      <c r="N23" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0972599999999999</v>
+      </c>
+      <c r="O23" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P23" s="2">
+        <f t="shared" si="0"/>
+        <v>2.6492599999999999</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2">
+        <f t="shared" si="1"/>
+        <v>-8.0039699999999991E-2</v>
+      </c>
+      <c r="S23" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.1162E-2</v>
+      </c>
+      <c r="T23" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="2">
+        <f t="shared" si="1"/>
+        <v>-8.0562199999999997</v>
+      </c>
+      <c r="W23" s="3">
+        <f t="shared" si="3"/>
+        <v>3.7569848000000006</v>
+      </c>
+      <c r="X23" s="3">
+        <f t="shared" si="3"/>
+        <v>5.9754638</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="3"/>
+        <v>-5.4673561999999993</v>
+      </c>
+      <c r="Z23" s="3">
+        <f t="shared" si="3"/>
+        <v>-11.607316200000005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1">
+        <v>256668</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1009840</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2630080</v>
+      </c>
+      <c r="G24" s="1">
+        <v>-38506.400000000001</v>
+      </c>
+      <c r="H24">
+        <v>152247</v>
+      </c>
+      <c r="J24" s="1">
+        <v>-7630630</v>
+      </c>
+      <c r="L24">
+        <v>21</v>
+      </c>
+      <c r="M24" s="2">
+        <f t="shared" si="0"/>
+        <v>0.25666800000000001</v>
+      </c>
+      <c r="N24" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0098400000000001</v>
+      </c>
+      <c r="O24" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="2">
+        <f t="shared" si="0"/>
+        <v>2.63008</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2">
+        <f t="shared" si="1"/>
+        <v>-3.8506400000000003E-2</v>
+      </c>
+      <c r="S24" s="2">
+        <f t="shared" si="1"/>
+        <v>0.15224699999999999</v>
+      </c>
+      <c r="T24" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="2">
+        <f t="shared" si="1"/>
+        <v>-7.63063</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>159832</v>
+      </c>
+      <c r="C25" s="1">
+        <v>920484</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2610170</v>
+      </c>
+      <c r="G25" s="1">
+        <v>-14791.5</v>
+      </c>
+      <c r="H25">
+        <v>288823</v>
+      </c>
+      <c r="J25" s="1">
+        <v>-7243350</v>
+      </c>
+      <c r="L25">
+        <v>22</v>
+      </c>
+      <c r="M25" s="2">
+        <f t="shared" si="0"/>
+        <v>0.159832</v>
+      </c>
+      <c r="N25" s="2">
+        <f t="shared" si="0"/>
+        <v>0.92048399999999997</v>
+      </c>
+      <c r="O25" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P25" s="2">
+        <f t="shared" si="0"/>
+        <v>2.6101700000000001</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.4791500000000001E-2</v>
+      </c>
+      <c r="S25" s="2">
+        <f t="shared" si="1"/>
+        <v>0.288823</v>
+      </c>
+      <c r="T25" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="2">
+        <f t="shared" si="1"/>
+        <v>-7.2433500000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>67113.899999999994</v>
+      </c>
+      <c r="C26" s="1">
+        <v>835318</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2595680</v>
+      </c>
+      <c r="G26" s="1">
+        <v>-5660.72</v>
+      </c>
+      <c r="H26">
+        <v>402467</v>
+      </c>
+      <c r="J26" s="1">
+        <v>-6890210</v>
+      </c>
+      <c r="L26">
+        <v>23</v>
+      </c>
+      <c r="M26" s="2">
+        <f t="shared" si="0"/>
+        <v>6.711389999999999E-2</v>
+      </c>
+      <c r="N26" s="2">
+        <f t="shared" si="0"/>
+        <v>0.835318</v>
+      </c>
+      <c r="O26" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="2">
+        <f t="shared" si="0"/>
+        <v>2.5956800000000002</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="5">
+        <f t="shared" si="1"/>
+        <v>-5.6607200000000002E-3</v>
+      </c>
+      <c r="S26" s="5">
+        <f t="shared" si="1"/>
+        <v>0.40246700000000002</v>
+      </c>
+      <c r="T26" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="5">
+        <f t="shared" si="1"/>
+        <v>-6.8902099999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>-27671</v>
+      </c>
+      <c r="C27" s="1">
+        <v>748154</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2580430</v>
+      </c>
+      <c r="G27" s="1">
+        <v>-9112.57</v>
+      </c>
+      <c r="H27">
+        <v>495796</v>
+      </c>
+      <c r="J27" s="1">
+        <v>-6568310</v>
+      </c>
+      <c r="L27">
+        <v>24</v>
+      </c>
+      <c r="M27" s="2">
+        <f t="shared" si="0"/>
+        <v>-2.7671000000000001E-2</v>
+      </c>
+      <c r="N27" s="2">
+        <f t="shared" si="0"/>
+        <v>0.74815399999999999</v>
+      </c>
+      <c r="O27" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="2">
+        <f t="shared" si="0"/>
+        <v>2.5804299999999998</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2">
+        <f t="shared" si="1"/>
+        <v>-9.1125700000000004E-3</v>
+      </c>
+      <c r="S27" s="2">
+        <f t="shared" si="1"/>
+        <v>0.49579600000000001</v>
+      </c>
+      <c r="T27" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="2">
+        <f t="shared" si="1"/>
+        <v>-6.5683100000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" s="1">
+        <v>555286</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1338800</v>
+      </c>
+      <c r="E28" s="1">
+        <v>3244240</v>
+      </c>
+      <c r="G28" s="1">
+        <v>54402.9</v>
+      </c>
+      <c r="H28">
+        <v>648933</v>
+      </c>
+      <c r="J28" s="1">
+        <v>-6197220</v>
+      </c>
+      <c r="L28">
+        <v>25</v>
+      </c>
+      <c r="M28" s="2">
+        <f t="shared" si="0"/>
+        <v>0.55528599999999995</v>
+      </c>
+      <c r="N28" s="2">
+        <f t="shared" si="0"/>
+        <v>1.3388</v>
+      </c>
+      <c r="O28" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P28" s="2">
+        <f t="shared" si="0"/>
+        <v>3.24424</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2">
+        <f t="shared" si="1"/>
+        <v>5.4402900000000004E-2</v>
+      </c>
+      <c r="S28" s="2">
+        <f t="shared" si="1"/>
+        <v>0.64893299999999998</v>
+      </c>
+      <c r="T28" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="2">
+        <f t="shared" si="1"/>
+        <v>-6.1972199999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="J33" t="s">
+        <v>11</v>
+      </c>
+      <c r="K33" t="s">
+        <v>13</v>
+      </c>
+      <c r="L33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1">
+        <v>-13557300</v>
+      </c>
+      <c r="L34" s="1">
+        <v>-13557300</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B35">
+        <v>4.3</v>
+      </c>
+      <c r="C35">
+        <v>2.1</v>
+      </c>
+      <c r="D35">
+        <v>0.7</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
+      <c r="K35" s="1">
+        <v>-4423200</v>
+      </c>
+      <c r="L35" s="1">
+        <v>9961670</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="J36">
+        <v>3</v>
+      </c>
+      <c r="K36" s="1">
+        <v>-2528160</v>
+      </c>
+      <c r="L36" s="1">
+        <v>2253980</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C37" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37">
+        <v>4</v>
+      </c>
+      <c r="K37" s="1">
+        <v>-1520630</v>
+      </c>
+      <c r="L37" s="1">
+        <v>1306930</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>5</v>
+      </c>
+      <c r="K38" s="1">
+        <v>-1042570</v>
+      </c>
+      <c r="L38" s="1">
+        <v>676313</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B39">
+        <f>B38+1</f>
+        <v>2</v>
+      </c>
+      <c r="C39">
+        <v>0.8</v>
+      </c>
+      <c r="D39">
+        <f>C39</f>
+        <v>0.8</v>
+      </c>
+      <c r="F39">
+        <f>C39</f>
+        <v>0.8</v>
+      </c>
+      <c r="J39">
+        <v>6</v>
+      </c>
+      <c r="K39" s="1">
+        <v>-703987</v>
+      </c>
+      <c r="L39" s="1">
+        <v>522382</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B40">
+        <f t="shared" ref="B40:B79" si="4">B39+1</f>
+        <v>3</v>
+      </c>
+      <c r="C40">
+        <v>1.6</v>
+      </c>
+      <c r="D40">
+        <f t="shared" ref="D40:F49" si="5">C40</f>
+        <v>1.6</v>
+      </c>
+      <c r="F40">
+        <f t="shared" ref="F40:F49" si="6">C40</f>
+        <v>1.6</v>
+      </c>
+      <c r="J40">
+        <v>7</v>
+      </c>
+      <c r="K40" s="1">
+        <v>-702556</v>
+      </c>
+      <c r="L40" s="1">
+        <v>2407.9699999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B41">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="C41">
+        <v>2.9</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="5"/>
+        <v>2.9</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="6"/>
+        <v>2.9</v>
+      </c>
+      <c r="J41">
+        <v>8</v>
+      </c>
+      <c r="K41">
+        <v>-987222</v>
+      </c>
+      <c r="L41" s="1">
+        <v>-522389</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B42">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="C42">
+        <v>4.2</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="5"/>
+        <v>4.2</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="6"/>
+        <v>4.2</v>
+      </c>
+      <c r="J42">
+        <v>9</v>
+      </c>
+      <c r="K42" s="1">
+        <v>-1332610</v>
+      </c>
+      <c r="L42" s="1">
+        <v>-691240</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B43">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="C43">
+        <v>5.6</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="5"/>
+        <v>5.6</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="6"/>
+        <v>5.6</v>
+      </c>
+      <c r="J43">
+        <v>10</v>
+      </c>
+      <c r="K43" s="1">
+        <v>-1729280</v>
+      </c>
+      <c r="L43" s="1">
+        <v>-865807</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B44">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="C44">
+        <v>9.1</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="5"/>
+        <v>9.1</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="6"/>
+        <v>9.1</v>
+      </c>
+      <c r="J44" s="1">
+        <v>11</v>
+      </c>
+      <c r="K44" s="1">
+        <v>-2168900</v>
+      </c>
+      <c r="L44" s="1">
+        <v>-1046480</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B45">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="C45">
+        <v>28</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="J45" s="1">
+        <v>12</v>
+      </c>
+      <c r="K45" s="1">
+        <v>-11035600</v>
+      </c>
+      <c r="L45" s="1">
+        <v>-23018800</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B46">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="C46">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="5"/>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="6"/>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="J46" s="1">
+        <v>13</v>
+      </c>
+      <c r="K46" s="1">
+        <v>-14594800</v>
+      </c>
+      <c r="L46" s="1">
+        <v>-10077300</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B47">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="C47">
+        <f t="shared" ref="C47:C52" si="7">C46+$B$35</f>
+        <v>41.099999999999994</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="5"/>
+        <v>41.099999999999994</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="6"/>
+        <v>41.099999999999994</v>
+      </c>
+      <c r="J47" s="1">
+        <v>14</v>
+      </c>
+      <c r="K47" s="1">
+        <v>-13706600</v>
+      </c>
+      <c r="L47" s="1">
+        <v>2742620</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B48">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="7"/>
+        <v>45.399999999999991</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="5"/>
+        <v>45.399999999999991</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="6"/>
+        <v>45.399999999999991</v>
+      </c>
+      <c r="J48">
+        <v>15</v>
+      </c>
+      <c r="K48" s="1">
+        <v>-12894700</v>
+      </c>
+      <c r="L48" s="1">
+        <v>2734160</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B49">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="7"/>
+        <v>49.699999999999989</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="5"/>
+        <v>49.699999999999989</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="6"/>
+        <v>49.699999999999989</v>
+      </c>
+      <c r="J49">
+        <v>16</v>
+      </c>
+      <c r="K49" s="1">
+        <v>-12152700</v>
+      </c>
+      <c r="L49" s="1">
+        <v>2725150</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B50" s="7">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="C50" s="7">
+        <f>C49+$C$35</f>
+        <v>51.79999999999999</v>
+      </c>
+      <c r="D50" s="7">
+        <f>C50-20</f>
+        <v>31.79999999999999</v>
+      </c>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7">
+        <v>0</v>
+      </c>
+      <c r="G50" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50">
+        <v>17</v>
+      </c>
+      <c r="K50" s="1">
+        <v>-11477400</v>
+      </c>
+      <c r="L50" s="1">
+        <v>2704980</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B51">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="C51">
+        <f t="shared" ref="C51:C63" si="8">C50+$C$35</f>
+        <v>53.899999999999991</v>
+      </c>
+      <c r="D51" s="6">
+        <f t="shared" ref="D51:D63" si="9">C51-20</f>
+        <v>33.899999999999991</v>
+      </c>
+      <c r="E51" s="6"/>
+      <c r="F51">
+        <f>D35</f>
+        <v>0.7</v>
+      </c>
+      <c r="J51">
+        <v>18</v>
+      </c>
+      <c r="K51" s="1">
+        <v>-10862900</v>
+      </c>
+      <c r="L51" s="1">
+        <v>2684220</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B52">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="8"/>
+        <v>55.999999999999993</v>
+      </c>
+      <c r="D52" s="6">
+        <f t="shared" si="9"/>
+        <v>35.999999999999993</v>
+      </c>
+      <c r="E52" s="6"/>
+      <c r="F52">
+        <f>F51+$D$35</f>
+        <v>1.4</v>
+      </c>
+      <c r="J52">
+        <v>19</v>
+      </c>
+      <c r="K52" s="1">
+        <v>-10301800</v>
+      </c>
+      <c r="L52" s="1">
+        <v>2673250</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B53">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="8"/>
+        <v>58.099999999999994</v>
+      </c>
+      <c r="D53" s="6">
+        <f t="shared" si="9"/>
+        <v>38.099999999999994</v>
+      </c>
+      <c r="E53" s="6"/>
+      <c r="F53">
+        <f>F52+$D$35</f>
+        <v>2.0999999999999996</v>
+      </c>
+      <c r="J53">
+        <v>20</v>
+      </c>
+      <c r="K53" s="1">
+        <v>-9789500</v>
+      </c>
+      <c r="L53" s="1">
+        <v>2661600</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B54">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="8"/>
+        <v>60.199999999999996</v>
+      </c>
+      <c r="D54" s="6">
+        <f t="shared" si="9"/>
+        <v>40.199999999999996</v>
+      </c>
+      <c r="E54" s="6"/>
+      <c r="F54">
+        <f>F53+$D$35</f>
+        <v>2.8</v>
+      </c>
+      <c r="J54" s="1">
+        <v>21</v>
+      </c>
+      <c r="K54" s="1">
+        <v>-9321960</v>
+      </c>
+      <c r="L54" s="1">
+        <v>2649260</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B55">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="8"/>
+        <v>62.3</v>
+      </c>
+      <c r="D55" s="6">
+        <f t="shared" si="9"/>
+        <v>42.3</v>
+      </c>
+      <c r="E55" s="6"/>
+      <c r="F55">
+        <f>F54+$D$35</f>
+        <v>3.5</v>
+      </c>
+      <c r="J55" s="1">
+        <v>22</v>
+      </c>
+      <c r="K55" s="1">
+        <v>-8896370</v>
+      </c>
+      <c r="L55" s="1">
+        <v>2630080</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B56">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="8"/>
+        <v>64.399999999999991</v>
+      </c>
+      <c r="D56" s="6">
+        <f t="shared" si="9"/>
+        <v>44.399999999999991</v>
+      </c>
+      <c r="E56" s="6"/>
+      <c r="F56">
+        <f>F55+$D$35</f>
+        <v>4.2</v>
+      </c>
+      <c r="J56">
+        <v>23</v>
+      </c>
+      <c r="K56" s="1">
+        <v>-8509080</v>
+      </c>
+      <c r="L56" s="1">
+        <v>2610170</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B57">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="8"/>
+        <v>66.499999999999986</v>
+      </c>
+      <c r="D57" s="6">
+        <f t="shared" si="9"/>
+        <v>46.499999999999986</v>
+      </c>
+      <c r="E57" s="6"/>
+      <c r="F57">
+        <f>F56+$D$35</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J57" s="1">
+        <v>24</v>
+      </c>
+      <c r="K57" s="1">
+        <v>-8155950</v>
+      </c>
+      <c r="L57" s="1">
+        <v>2595680</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B58">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="8"/>
+        <v>68.59999999999998</v>
+      </c>
+      <c r="D58" s="6">
+        <f t="shared" si="9"/>
+        <v>48.59999999999998</v>
+      </c>
+      <c r="E58" s="6"/>
+      <c r="F58">
+        <f>F57+$D$35</f>
+        <v>5.6000000000000005</v>
+      </c>
+      <c r="J58" s="1">
+        <v>25</v>
+      </c>
+      <c r="K58" s="1">
+        <v>-7834050</v>
+      </c>
+      <c r="L58" s="1">
+        <v>2580430</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B59">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="8"/>
+        <v>70.699999999999974</v>
+      </c>
+      <c r="D59" s="6">
+        <f t="shared" si="9"/>
+        <v>50.699999999999974</v>
+      </c>
+      <c r="E59" s="6"/>
+      <c r="F59">
+        <f>F58+$D$35</f>
+        <v>6.3000000000000007</v>
+      </c>
+      <c r="J59" s="1">
+        <v>26</v>
+      </c>
+      <c r="K59" s="1">
+        <v>-7462960</v>
+      </c>
+      <c r="L59" s="1">
+        <v>3244240</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B60">
+        <f t="shared" si="4"/>
+        <v>23</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="8"/>
+        <v>72.799999999999969</v>
+      </c>
+      <c r="D60" s="6">
+        <f t="shared" si="9"/>
+        <v>52.799999999999969</v>
+      </c>
+      <c r="E60" s="6"/>
+      <c r="F60">
+        <f>F59+$D$35</f>
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B61">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="8"/>
+        <v>74.899999999999963</v>
+      </c>
+      <c r="D61" s="6">
+        <f t="shared" si="9"/>
+        <v>54.899999999999963</v>
+      </c>
+      <c r="E61" s="6"/>
+      <c r="F61">
+        <f>F60+$D$35</f>
+        <v>7.7000000000000011</v>
+      </c>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B62">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="8"/>
+        <v>76.999999999999957</v>
+      </c>
+      <c r="D62" s="6">
+        <f t="shared" si="9"/>
+        <v>56.999999999999957</v>
+      </c>
+      <c r="E62" s="6"/>
+      <c r="F62">
+        <f>F61+$D$35</f>
+        <v>8.4</v>
+      </c>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B63">
+        <f t="shared" si="4"/>
+        <v>26</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="8"/>
+        <v>79.099999999999952</v>
+      </c>
+      <c r="D63" s="6">
+        <f t="shared" si="9"/>
+        <v>59.099999999999952</v>
+      </c>
+      <c r="E63" s="6"/>
+      <c r="F63">
+        <f>F62+$D$35</f>
+        <v>9.1</v>
+      </c>
+      <c r="J63" s="1"/>
+    </row>
+    <row r="64" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B64">
+        <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="F64">
+        <f>F63+$D$35</f>
+        <v>9.7999999999999989</v>
+      </c>
+      <c r="J64" s="1"/>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B65">
+        <f t="shared" si="4"/>
+        <v>28</v>
+      </c>
+      <c r="F65">
+        <f>F64+$D$35</f>
+        <v>10.499999999999998</v>
+      </c>
+      <c r="J65" s="1"/>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B66">
+        <f t="shared" si="4"/>
+        <v>29</v>
+      </c>
+      <c r="F66">
+        <f>F65+$D$35</f>
+        <v>11.199999999999998</v>
+      </c>
+      <c r="J66" s="1"/>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B67">
+        <f t="shared" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="F67">
+        <f>F66+$D$35</f>
+        <v>11.899999999999997</v>
+      </c>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B68">
+        <f t="shared" si="4"/>
+        <v>31</v>
+      </c>
+      <c r="F68">
+        <f>F67+$D$35</f>
+        <v>12.599999999999996</v>
+      </c>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A788E4FEB44D0B4CB1AD2E9A3A83F076" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1d34d9b8e131c103df8a093e310b027">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8baa01ab-7cf8-4360-9f3f-f87b1ec95c26" xmlns:ns3="d481fc2a-e230-47f7-a716-4f7f4b27a8e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c44e149c0724d485dcb6f09127e30ffd" ns2:_="" ns3:_="">
     <xsd:import namespace="8baa01ab-7cf8-4360-9f3f-f87b1ec95c26"/>
@@ -5719,26 +11853,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A82D478-F143-4E1A-BE03-DF93E0476218}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8baa01ab-7cf8-4360-9f3f-f87b1ec95c26"/>
-    <ds:schemaRef ds:uri="d481fc2a-e230-47f7-a716-4f7f4b27a8e6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB2C9E99-917F-4BDF-B9E4-ADA5D0AFF133}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8baa01ab-7cf8-4360-9f3f-f87b1ec95c26">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d481fc2a-e230-47f7-a716-4f7f4b27a8e6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F33A64FD-BD8E-4A10-881A-543F22FB0B66}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5757,6 +11892,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB2C9E99-917F-4BDF-B9E4-ADA5D0AFF133}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A82D478-F143-4E1A-BE03-DF93E0476218}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8baa01ab-7cf8-4360-9f3f-f87b1ec95c26"/>
+    <ds:schemaRef ds:uri="d481fc2a-e230-47f7-a716-4f7f4b27a8e6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{95965d95-ecc0-4720-b759-1f33c42ed7da}" enabled="1" method="Standard" siteId="{a0f29d7e-28cd-4f54-8442-7885aee7c080}" removed="0"/>
